--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -4580,7 +4580,7 @@
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>rd_act_m[e] = !r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; r_bank_act_ready[rb] &amp;&amp; tfaw_ok_i &amp;&amp; trrd_ok_i &amp;&amp; !w_rfc_busy   [wr_act_m[e] is the same with wb for rb]</t>
+          <t>rd_act_m[e] = !r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; r_bank_act_ready[rb] &amp;&amp; w_act_classify_gate &amp;&amp; !w_rfc_busy   [w_act_classify_gate folds tfaw_ok_i &amp;&amp; trrd_ok_i; r_bank_act_ready samples the ADVISORY lookahead twin (bank_act_ready_la_i), the live set being enforced at the final stage -- see w_out_ready. wr_act_m[e] is the same with wb for rb]</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
     <row r="221">
       <c r="A221" s="18" t="inlineStr">
         <is>
-          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | w_prepick_guard[b] | w_col_inflight_guard[b] | ((w_inflight_preact || w_inflight_col) &amp;&amp; (r_bank == b))   [guards_nz = w_prepick_guard[b] | w_col_inflight_guard[b]; bank_match = r_bank==b]</t>
+          <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | w_prepick_guard[b] | w_col_inflight_guard[b] | w_if_preact_out[b] | w_if_col_out[b]   [guards_nz = w_prepick_guard[b] | w_col_inflight_guard[b]; bank_match = w_if_preact_out[b] | w_if_col_out[b], the in-flight shadow's OUT stage -- each is (inflight_class ? 1&lt;&lt;r_bank : 0), so their OR is the old ((preact||col) &amp;&amp; r_bank==b) term by construction]</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
     <row r="251">
       <c r="A251" s="18" t="inlineStr">
         <is>
-          <t>w_out_ready = !r_pick_valid || cmd_ready_i ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i</t>
+          <t>w_out_ready = !r_pick_valid || cmd_ready_i || w_out_reject ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i &amp;&amp; w_out_safe   [w_out_safe = the LIVE bank readiness for the op in the output register; w_out_reject = r_pick_valid &amp;&amp; !w_out_safe. A rejected pick is DROPPED, not held -- holding freezes w_out_ready and head-of-line blocks the pipeline. cmd_ready is folded to (cmd_ready_i &amp;&amp; w_out_safe) for this map's axes]</t>
         </is>
       </c>
     </row>

--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +74,14 @@
     <font>
       <i val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -109,7 +117,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE68A"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -145,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,12 +197,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -204,9 +213,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2719,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2780,1175 +2790,1213 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: EXACTLY ONE 1-cell, at all-zeros (on the grant=0 page; the grant=1 page is all-zero because a REF already granted this cycle must not re-arm). Any additional 1 is a hole that lets REFab collide with an open/opening row or violate tRFC (the silicon row-corruption bug class).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    any_active</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>|r_bank_row_active[RK0]</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:1052</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    inflight_preact</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>r_pick_valid &amp;&amp; (r_do_act || r_do_pre)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:302</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    guards_nz</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>(r_guard0 != '0) || (r_guard1 != '0)</t>
+          <t>any_active</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>|r_bank_row_active[RK0]</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv (guard stages)</t>
+          <t>pumice_cmd_arbiter.sv:1052</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    rfc_busy</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>w_rfc_busy -- r_rfc_cnt != 0, reloaded on each fired REF</t>
+          <t>inflight_preact</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>r_pick_valid &amp;&amp; (r_do_act || r_do_pre)</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv</t>
+          <t>pumice_cmd_arbiter.sv:302</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    grant</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+          <t>guards_nz</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>(r_guard0 != '0) || (r_guard1 != '0)</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard stages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>rfc_busy</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>w_rfc_busy -- r_rfc_cnt != 0, reloaded on each fired REF</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>r_grant -- a REF was granted this cycle</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (independent) guards_nz and inflight_preact overlap in meaning but not in value: a pick in flight sets a guard only from the NEXT cycle, so all four combinations occur.</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (r_guard0/1 are registered off the pick)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: EXACTLY ONE 1-cell, at all-zeros (on the grant=0 page; the grant=1 page is all-zero because a REF already granted this cycle must not re-arm). Any additional 1 is a hole that lets REFab collide with an open/opening row or violate tRFC (the silicon row-corruption bug class).</t>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) guards_nz and inflight_preact overlap in meaning but not in value: a pick in flight sets a guard only from the NEXT cycle, so all four combinations occur.</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (r_guard0/1 are registered off the pick)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>[grant=0]</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="21" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B22" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="C22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="B23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="B24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="B25" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>[grant=1]</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="21" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="B29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="B30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="B31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    !any_active &amp; !inflight_preact &amp; !guards_nz &amp; !rfc_busy &amp; !grant</t>
-        </is>
+      <c r="B32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !any_active &amp; !inflight_preact &amp; !guards_nz &amp; !rfc_busy &amp; !grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>refresh-branch action (given refresh_req_i||refresh_drain_i)</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (priority 2)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>if (any_active) { if (rfsh_pre_found) PRE else wait } else if (ref_safe) REF else wait</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>rows = any_active/rfsh_pre_found   cols = ref_safe</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    any_active</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: REF appears ONLY where any_active=0 AND ref_safe=1. PRE only where any_active=1 AND pre_found=1. Everything else waits (the branch never falls through to column/ACT picks).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>any_active</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>|r_bank_row_active[RK0]</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:1052</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rfsh_pre_found</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>rfsh_pre_found</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>any j with r_bank_row_active[j] &amp;&amp; r_bank_pre_ready[j] &amp;&amp; !w_guarded[j]</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:1054-1058</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ref_safe</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>ref_safe</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>w_ref_safe -- see its own map above</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (refresh pick gate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ref_safe =&gt; !any_active. w_ref_safe is literally ANDed with !w_any_active, so the two cannot both be 1 -- half this grid cannot occur.</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (w_ref_safe = !w_any_active &amp;&amp; ...)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rfsh_pre_found =&gt; any_active. The search only sets it for a bank with r_bank_row_active[j] high, so 'a bank to precharge exists' implies 'a row is open'.</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:1054-1058</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: REF appears ONLY where any_active=0 AND ref_safe=1. PRE only where any_active=1 AND pre_found=1. Everything else waits (the branch never falls through to column/ACT picks).</t>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ref_safe =&gt; !any_active. w_ref_safe is literally ANDed with !w_any_active, so the two cannot both be 1 -- half this grid cannot occur.</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (w_ref_safe = !w_any_active &amp;&amp; ...)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rfsh_pre_found =&gt; any_active. The search only sets it for a bank with r_bank_row_active[j] high, so 'a bank to precharge exists' implies 'a row is open'.</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:1054-1058</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B49" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B53" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C53" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B51" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="21" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B52" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>cells: 4 reachable, 4 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>rd_col_m[e] = rhit &amp;&amp; r_bank_rdwr_ready[rb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; twtr_ok_i &amp;&amp; rd_issue_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [rd_issue_ready_i factored out as the enabling condition; dbl_issue = (f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]; col_guard = r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]]</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>rd_col_m[e] = rhit &amp;&amp; r_bank_rdwr_ready[rb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; twtr_ok_i &amp;&amp; rd_issue_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [rd_issue_ready_i factored out as the enabling condition; dbl_issue = (f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]; col_guard = r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]]</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = dbl_issue/col_guard</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = dbl_issue/col_guard</t>
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [dbl_issue=0, col_guard=0], single all-ones cell. A 1 anywhere on a col_guard=1 page would mean a RD issued through a turnaround/AP/precharge guard -- the class that produced the 471/471 concurrent-soak corruption (a RD into a write burst's DQ occupancy on a stale flopped twtr_ok).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
+          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rhit</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>r_bank_row_active[RK0][rb] &amp;&amp; (row == r_bank_open_row[RK0][rb])</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:562-563</t>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    rdwr_ready</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>r_bank_rdwr_ready[RK0][rb] = safe_rd_o = r_row_valid &amp;&amp; (r_rcd=='0) &amp;&amp; !r_ap_pending</t>
+          <t>rhit</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>r_bank_row_active[RK0][rb] &amp;&amp; (row == r_bank_open_row[RK0][rb])</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>bank_timer.sv:135</t>
+          <t>pumice_cmd_arbiter.sv:562-563</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tccd_ok</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>w_tccd_fwd_ok -- FORWARD tCCD at classify time, not the flopped tccd_ok_i</t>
+          <t>rdwr_ready</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>r_bank_rdwr_ready[RK0][rb] = safe_rd_o = r_row_valid &amp;&amp; (r_rcd=='0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv:420-432</t>
+          <t>bank_timer.sv:135</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    twtr_ok</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>twtr_ok_i -- write-to-read turnaround, from global_timers</t>
+          <t>tccd_ok</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>w_tccd_fwd_ok -- FORWARD tCCD at classify time, not the flopped tccd_ok_i</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>global_timers.sv</t>
+          <t>pumice_cmd_arbiter.sv:420-432</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    dbl_issue</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>(f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]</t>
+          <t>twtr_ok</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>twtr_ok_i -- write-to-read turnaround, from global_timers</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv:361-371,383-385</t>
+          <t>global_timers.sv</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    col_guard</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
+          <t>dbl_issue</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>(f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:361-371,383-385</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>col_guard</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
         <is>
           <t>r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:574-580</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
     <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) rhit and rdwr_ready both require an open row but neither implies the other: a hit can be pending tRCD (rdwr_ready=0), and a ready bank can hold the WRONG row (rhit=0). All four occur.</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:562-565 + bank_timer.sv:135</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [dbl_issue=0, col_guard=0], single all-ones cell. A 1 anywhere on a col_guard=1 page would mean a RD issued through a turnaround/AP/precharge guard -- the class that produced the 471/471 concurrent-soak corruption (a RD into a write burst's DQ occupancy on a stale flopped twtr_ok).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="21" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="21" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C74" s="21" t="inlineStr">
+      <c r="C75" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D74" s="21" t="inlineStr">
+      <c r="D75" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E74" s="21" t="inlineStr">
+      <c r="E75" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="21" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="21" t="inlineStr">
+      <c r="B76" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B76" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="inlineStr">
+      <c r="B77" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B77" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="22" t="n">
+      <c r="B78" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="21" t="inlineStr">
+      <c r="E78" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B78" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="B79" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="21" t="inlineStr">
+    <row r="82">
+      <c r="B82" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C81" s="21" t="inlineStr">
+      <c r="C82" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D81" s="21" t="inlineStr">
+      <c r="D82" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E81" s="21" t="inlineStr">
+      <c r="E82" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="21" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B82" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="21" t="inlineStr">
+      <c r="B83" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B83" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="21" t="inlineStr">
+      <c r="B84" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B84" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="21" t="inlineStr">
+      <c r="B85" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B85" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="B86" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="21" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C88" s="21" t="inlineStr">
+      <c r="C89" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D88" s="21" t="inlineStr">
+      <c r="D89" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E88" s="21" t="inlineStr">
+      <c r="E89" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="21" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B89" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="21" t="inlineStr">
+      <c r="B90" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B90" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="21" t="inlineStr">
+      <c r="B91" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B91" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="21" t="inlineStr">
+      <c r="B92" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B92" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="B93" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="21" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C95" s="21" t="inlineStr">
+      <c r="C96" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D95" s="21" t="inlineStr">
+      <c r="D96" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E95" s="21" t="inlineStr">
+      <c r="E96" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="21" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B96" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="21" t="inlineStr">
+      <c r="B97" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B97" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="inlineStr">
+      <c r="B98" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B98" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="21" t="inlineStr">
+      <c r="B99" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B99" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
+      <c r="B100" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rhit &amp; rdwr_ready &amp; tccd_ok &amp; twtr_ok &amp; !dbl_issue &amp; !col_guard</t>
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: rhit &amp; rdwr_ready &amp; tccd_ok &amp; twtr_ok &amp; !dbl_issue &amp; !col_guard</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
@@ -3981,2069 +4029,2132 @@
     <row r="108">
       <c r="A108" s="19" t="inlineStr">
         <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+          <t>CHECK BY INSPECTION: Exact mirror of rd_col_m with the write-side turnaround (trtw) and commit-ready: 1s only on [dbl_issue=0, col_guard=0].</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (independent) dbl_issue and col_guard are independent: the first is double-issue prevention for THIS entry/bank, the second folds turnaround, AP and precharge guards. Either can hold alone.</t>
-        </is>
-      </c>
-      <c r="D109" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:581-587</t>
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Exact mirror of rd_col_m with the write-side turnaround (trtw) and commit-ready: 1s only on [dbl_issue=0, col_guard=0].</t>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) dbl_issue and col_guard are independent: the first is double-issue prevention for THIS entry/bank, the second folds turnaround, AP and precharge guards. Either can hold alone.</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:581-587</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="A112" s="21" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="21" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C113" s="21" t="inlineStr">
+      <c r="C115" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D113" s="21" t="inlineStr">
+      <c r="D115" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E113" s="21" t="inlineStr">
+      <c r="E115" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="21" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B114" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="21" t="inlineStr">
+      <c r="B116" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="21" t="inlineStr">
+      <c r="B117" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B116" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="22" t="n">
+      <c r="B118" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E116" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="21" t="inlineStr">
+      <c r="E118" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B117" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="B119" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="21" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
+      <c r="C122" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D120" s="21" t="inlineStr">
+      <c r="D122" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E120" s="21" t="inlineStr">
+      <c r="E122" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="21" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B121" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="21" t="inlineStr">
+      <c r="B123" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B122" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="21" t="inlineStr">
+      <c r="B124" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="21" t="inlineStr">
+      <c r="B125" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="B126" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="B127" s="21" t="inlineStr">
+    <row r="129">
+      <c r="B129" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C127" s="21" t="inlineStr">
+      <c r="C129" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D127" s="21" t="inlineStr">
+      <c r="D129" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E127" s="21" t="inlineStr">
+      <c r="E129" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="21" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B128" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="21" t="inlineStr">
+      <c r="B130" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="21" t="inlineStr">
+      <c r="B131" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B130" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="21" t="inlineStr">
+      <c r="B132" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B131" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="B133" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="B134" s="21" t="inlineStr">
+    <row r="136">
+      <c r="B136" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C134" s="21" t="inlineStr">
+      <c r="C136" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D134" s="21" t="inlineStr">
+      <c r="D136" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E134" s="21" t="inlineStr">
+      <c r="E136" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="21" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B135" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="21" t="inlineStr">
+      <c r="B137" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B136" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="21" t="inlineStr">
+      <c r="B138" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B137" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="21" t="inlineStr">
+      <c r="B139" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B138" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    whit &amp; rdwr_ready &amp; tccd_ok &amp; trtw_ok &amp; !dbl_issue &amp; !col_guard</t>
-        </is>
+      <c r="B140" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="15" t="inlineStr">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: whit &amp; rdwr_ready &amp; tccd_ok &amp; trtw_ok &amp; !dbl_issue &amp; !col_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="inlineStr">
         <is>
           <t>w_rd_turn_block / w_wr_turn_block</t>
         </is>
       </c>
-      <c r="D144" s="17" t="inlineStr">
+      <c r="D145" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (direction-turnaround guard)</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="18" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="18" t="inlineStr">
         <is>
           <t>w_rd_turn_block = r_wrfire0 || r_wrfire1 ; w_wr_turn_block = r_rdfire0 || r_rdfire1   (fire-shift of the OPPOSITE direction; covers the 2 cycles until the flopped twtr/trtw ok reflects the fired column)</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = oppfire0/oppfire1   cols = </t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
     <row r="148">
-      <c r="A148" s="16" t="inlineStr">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) The two fire flags are consecutive pipeline stages of the same event, so all four combinations occur as a fired column walks through: 01 means 'fired last cycle', 11 'two back to back'.</t>
         </is>
       </c>
-      <c r="D148" s="17" t="inlineStr">
+      <c r="D151" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (r_wrfire0/r_wrfire1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="22" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B152" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="21" t="inlineStr">
+      <c r="B155" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B153" s="22" t="n">
+      <c r="B156" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="21" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B154" s="22" t="n">
+      <c r="B157" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="21" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B155" s="22" t="n">
+      <c r="B158" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    oppfire1  |  oppfire0</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+    <row r="160">
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: oppfire1  |  oppfire0</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="15" t="inlineStr">
+      <c r="A161" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="inlineStr">
         <is>
           <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D161" s="17" t="inlineStr">
+      <c r="D163" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="18" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
         <is>
           <t>rd_act_m[e] = !r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; r_bank_act_ready[rb] &amp;&amp; w_act_classify_gate &amp;&amp; !w_rfc_busy   [w_act_classify_gate folds tfaw_ok_i &amp;&amp; trrd_ok_i; r_bank_act_ready samples the ADVISORY lookahead twin (bank_act_ready_la_i), the live set being enforced at the final stage -- see w_out_ready. wr_act_m[e] is the same with wb for rb]</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="16" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    act_ready =&gt; !row_active. bank_act_ready is safe_act_o, which is ANDed with !r_row_valid -- a bank with a row open never reports itself ready to activate. Half the grid cannot occur.</t>
         </is>
       </c>
-      <c r="D165" s="17" t="inlineStr">
+      <c r="D169" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:133 (safe_act_o = !r_row_valid &amp;&amp; ...)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>[trrd_ok=0, rfc_busy=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C169" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D169" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E169" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>[trrd_ok=0, rfc_busy=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="22" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B170" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C170" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="21" t="inlineStr">
+      <c r="C173" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B171" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C171" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="21" t="inlineStr">
+      <c r="D173" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B172" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" s="24" t="inlineStr">
+      <c r="E173" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B174" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B175" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B176" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E172" s="24" t="inlineStr">
+      <c r="E176" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="21" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B173" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" s="24" t="inlineStr">
+      <c r="B177" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E173" s="24" t="inlineStr">
+      <c r="E177" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="8" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=0, rfc_busy=1]</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="B176" s="21" t="inlineStr">
+    <row r="180">
+      <c r="B180" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C176" s="21" t="inlineStr">
+      <c r="C180" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D176" s="21" t="inlineStr">
+      <c r="D180" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E176" s="21" t="inlineStr">
+      <c r="E180" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="21" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B177" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="21" t="inlineStr">
+      <c r="B181" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B178" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C178" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D178" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E178" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="21" t="inlineStr">
+      <c r="B182" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B179" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C179" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D179" s="24" t="inlineStr">
+      <c r="B183" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E179" s="24" t="inlineStr">
+      <c r="E183" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="21" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B180" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C180" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D180" s="24" t="inlineStr">
+      <c r="B184" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E180" s="24" t="inlineStr">
+      <c r="E184" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="8" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=1, rfc_busy=0]</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="B183" s="21" t="inlineStr">
+    <row r="187">
+      <c r="B187" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C183" s="21" t="inlineStr">
+      <c r="C187" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D183" s="21" t="inlineStr">
+      <c r="D187" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E183" s="21" t="inlineStr">
+      <c r="E187" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="21" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B184" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C184" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" s="22" t="n">
+      <c r="B188" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E184" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="21" t="inlineStr">
+      <c r="E188" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B185" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C185" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="21" t="inlineStr">
+      <c r="B189" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B186" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C186" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D186" s="24" t="inlineStr">
+      <c r="B190" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E186" s="24" t="inlineStr">
+      <c r="E190" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="21" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B187" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C187" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D187" s="24" t="inlineStr">
+      <c r="B191" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E187" s="24" t="inlineStr">
+      <c r="E191" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="8" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=1, rfc_busy=1]</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="B190" s="21" t="inlineStr">
+    <row r="194">
+      <c r="B194" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C190" s="21" t="inlineStr">
+      <c r="C194" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D190" s="21" t="inlineStr">
+      <c r="D194" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E190" s="21" t="inlineStr">
+      <c r="E194" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="21" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B191" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D191" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E191" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="21" t="inlineStr">
+      <c r="B195" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B192" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C192" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E192" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="21" t="inlineStr">
+      <c r="B196" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B193" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C193" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" s="24" t="inlineStr">
+      <c r="B197" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C197" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E193" s="24" t="inlineStr">
+      <c r="E197" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="21" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B194" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C194" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" s="24" t="inlineStr">
+      <c r="B198" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E194" s="24" t="inlineStr">
+      <c r="E198" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="20" t="inlineStr">
-        <is>
-          <t>cells: 48 reachable, 16 don't-care (X) of 64. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    !guarded &amp; act_ready &amp; tfaw_ok &amp; trrd_ok &amp; !rfc_busy</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !guarded &amp; act_ready &amp; tfaw_ok &amp; trrd_ok &amp; !rfc_busy</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="15" t="inlineStr">
+      <c r="A201" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 16 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="15" t="inlineStr">
         <is>
           <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D201" s="17" t="inlineStr">
+      <c r="D204" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify)</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="18" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
         <is>
           <t>rd_pre_m[e] = r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; !rhit &amp;&amp; r_bank_pre_ready[rb]   [wr_pre_m[e] is the same with wb/whit]</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = hit/pre_ready</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="16" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    hit =&gt; row_active. A row HIT is defined as 'this bank has a row open AND it is the requested one', so a hit with no open row is not a state the hardware can be in -- it is a contradiction in the term itself, not a case the logic happens to avoid.</t>
         </is>
       </c>
-      <c r="D205" s="17" t="inlineStr">
+      <c r="D210" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:562-565 (rhit/whit = r_bank_row_active[b] &amp;&amp; row==open_row)</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="16" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    pre_ready =&gt; row_active. safe_pre_o is ANDed with r_row_valid, so tRAS/tRTP/tWR clearance is only ever reported for a bank that has a row to precharge.</t>
         </is>
       </c>
-      <c r="D206" s="17" t="inlineStr">
+      <c r="D211" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:138 (safe_pre_o = r_row_valid &amp;&amp; (r_ras=='0) &amp;&amp; (r_preblk=='0) &amp;&amp; !r_ap_pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="B209" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C209" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D209" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E209" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B210" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C210" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D210" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E210" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B211" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C211" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D211" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E211" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C214" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D214" s="22" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B212" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C212" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D212" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E212" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="21" t="inlineStr">
+      <c r="E214" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B213" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C213" s="22" t="n">
+    </row>
+    <row r="215">
+      <c r="A215" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B215" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C215" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D215" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E215" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B216" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D216" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E216" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B217" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B218" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C218" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D213" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E213" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="20" t="inlineStr">
-        <is>
-          <t>cells: 10 reachable, 6 don't-care (X) of 16. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    !guarded &amp; !hit &amp; pre_ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
+      <c r="D218" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr">
+      <c r="A220" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !guarded &amp; !hit &amp; pre_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 6 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="15" t="inlineStr">
         <is>
           <t>w_guarded[b]</t>
         </is>
       </c>
-      <c r="D220" s="17" t="inlineStr">
+      <c r="D224" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="18" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="18" t="inlineStr">
         <is>
           <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | w_prepick_guard[b] | w_col_inflight_guard[b] | w_if_preact_out[b] | w_if_col_out[b]   [guards_nz = w_prepick_guard[b] | w_col_inflight_guard[b]; bank_match = w_if_preact_out[b] | w_if_col_out[b], the in-flight shadow's OUT stage -- each is (inflight_class ? 1&lt;&lt;r_bank : 0), so their OR is the old ((preact||col) &amp;&amp; r_bank==b) term by construction]</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>rows = guard0/guard1   cols = pick_guards_nz/inflight_rowop_or_col   pages = bank_match</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="8" t="inlineStr">
-        <is>
-          <t>AXIS TERMS -- each axis is itself a signal, with its own equation:</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    guard0 / guard1</t>
-        </is>
-      </c>
-      <c r="B224" s="16" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="17" t="inlineStr">
+        <is>
+          <t>guard0</t>
+        </is>
+      </c>
+      <c r="B230" s="18" t="inlineStr">
         <is>
           <t>r_guard0[b] / r_guard1[b] -- the two registered guard stages a pick walks through</t>
         </is>
       </c>
-      <c r="D224" s="17" t="inlineStr">
+      <c r="D230" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    pick_guards_nz</t>
-        </is>
-      </c>
-      <c r="B225" s="16" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="17" t="inlineStr">
+        <is>
+          <t>guard1</t>
+        </is>
+      </c>
+      <c r="B231" s="18" t="inlineStr">
+        <is>
+          <t>r_guard0[b] / r_guard1[b] -- the two registered guard stages a pick walks through</t>
+        </is>
+      </c>
+      <c r="D231" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="17" t="inlineStr">
+        <is>
+          <t>pick_guards_nz</t>
+        </is>
+      </c>
+      <c r="B232" s="18" t="inlineStr">
         <is>
           <t>w_prepick_guard[b] | w_col_inflight_guard[b]</t>
         </is>
       </c>
-      <c r="D225" s="17" t="inlineStr">
+      <c r="D232" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:346-350</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    inflight_rowop_or_col</t>
-        </is>
-      </c>
-      <c r="B226" s="16" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="17" t="inlineStr">
+        <is>
+          <t>inflight_rowop_or_col</t>
+        </is>
+      </c>
+      <c r="B233" s="18" t="inlineStr">
         <is>
           <t>w_inflight_preact || w_inflight_col</t>
         </is>
       </c>
-      <c r="D226" s="17" t="inlineStr">
+      <c r="D233" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:300-302</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    bank_match</t>
-        </is>
-      </c>
-      <c r="B227" s="16" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="17" t="inlineStr">
+        <is>
+          <t>bank_match</t>
+        </is>
+      </c>
+      <c r="B234" s="18" t="inlineStr">
         <is>
           <t>r_bank == b -- the in-flight pick targets THIS bank</t>
         </is>
       </c>
-      <c r="D227" s="17" t="inlineStr">
+      <c r="D234" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="16" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) The guard stages are a shift register, so guard0/guard1 take all four combinations as a pick moves through; bank_match is an address compare independent of all of them.</t>
         </is>
       </c>
-      <c r="D229" s="17" t="inlineStr">
+      <c r="D236" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="8" t="inlineStr">
-        <is>
-          <t>[bank_match=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="B233" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C233" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D233" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E233" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B234" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C234" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D234" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E234" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B235" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C235" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D235" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E235" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B236" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C236" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D236" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E236" s="22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B237" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C237" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D237" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E237" s="22" t="n">
-        <v>1</v>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="8" t="inlineStr">
         <is>
+          <t>[bank_match=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C240" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D240" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E240" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B241" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B242" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B243" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B244" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="8" t="inlineStr">
+        <is>
           <t>[bank_match=1]</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="B240" s="21" t="inlineStr">
+    <row r="247">
+      <c r="B247" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C240" s="21" t="inlineStr">
+      <c r="C247" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D240" s="21" t="inlineStr">
+      <c r="D247" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E240" s="21" t="inlineStr">
+      <c r="E247" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="21" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B241" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" s="22" t="n">
+      <c r="B248" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D241" s="22" t="n">
+      <c r="D248" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E241" s="22" t="n">
+      <c r="E248" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="21" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B242" s="22" t="n">
+      <c r="B249" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C242" s="22" t="n">
+      <c r="C249" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D242" s="22" t="n">
+      <c r="D249" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E242" s="22" t="n">
+      <c r="E249" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="21" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B243" s="22" t="n">
+      <c r="B250" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C243" s="22" t="n">
+      <c r="C250" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D243" s="22" t="n">
+      <c r="D250" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="22" t="n">
+      <c r="E250" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="21" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B244" s="22" t="n">
+      <c r="B251" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C244" s="22" t="n">
+      <c r="C251" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D244" s="22" t="n">
+      <c r="D251" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E244" s="22" t="n">
+      <c r="E251" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    pick_guards_nz  |  guard1  |  guard0  |  inflight_rowop_or_col &amp; bank_match</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="15" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: inflight_rowop_or_col &amp; bank_match  |  pick_guards_nz  |  guard1  |  guard0</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="15" t="inlineStr">
         <is>
           <t>w_out_ready / w_fire_out</t>
         </is>
       </c>
-      <c r="D250" s="17" t="inlineStr">
+      <c r="D256" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (output register)</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="18" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="18" t="inlineStr">
         <is>
           <t>w_out_ready = !r_pick_valid || cmd_ready_i || w_out_reject ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i &amp;&amp; w_out_safe   [w_out_safe = the LIVE bank readiness for the op in the output register; w_out_reject = r_pick_valid &amp;&amp; !w_out_safe. A rejected pick is DROPPED, not held -- holding freezes w_out_ready and head-of-line blocks the pipeline. cmd_ready is folded to (cmd_ready_i &amp;&amp; w_out_safe) for this map's axes]</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (independent) pick_valid is internal; cmd_ready_i belongs to the downstream FIFO. Nothing couples them, so all four occur -- which is what makes the pick pipeline latency rather than a rate limit.</t>
-        </is>
-      </c>
-      <c r="D254" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (output register)</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="20" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
         </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="B257" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B258" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B259" s="22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="21" t="inlineStr">
         <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) pick_valid is internal; cmd_ready_i belongs to the downstream FIFO. Nothing couples them, so all four occur -- which is what makes the pick pipeline latency rather than a rate limit.</t>
+        </is>
+      </c>
+      <c r="D262" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (output register)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="21" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B266" s="23" t="inlineStr">
+        <is>
+          <t>rdy</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B267" s="23" t="inlineStr">
+        <is>
+          <t>rdy</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="22" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B260" s="22" t="n">
+      <c r="B268" s="23" t="inlineStr">
+        <is>
+          <t>rdy+fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B269" s="24" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="inlineStr">
+        <is>
+          <t>pick priority (strict, first match wins)</t>
+        </is>
+      </c>
+      <c r="D272" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="19" t="inlineStr">
+        <is>
+          <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="27" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B274" s="27" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C274" s="27" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D274" s="27" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="28" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B261" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="15" t="inlineStr">
-        <is>
-          <t>pick priority (strict, first match wins)</t>
-        </is>
-      </c>
-      <c r="D267" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="20" t="inlineStr">
-        <is>
-          <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="25" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B269" s="25" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="C269" s="25" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="D269" s="25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B270" s="26" t="inlineStr">
+      <c r="B275" s="28" t="inlineStr">
         <is>
           <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
         </is>
       </c>
-      <c r="C270" s="26" t="inlineStr">
+      <c r="C275" s="28" t="inlineStr">
         <is>
           <t>forward init op</t>
         </is>
       </c>
-      <c r="D270" s="26" t="inlineStr">
+      <c r="D275" s="28" t="inlineStr">
         <is>
           <t>MRS/PRE/REF from init_sequencer verbatim</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="26" t="n">
+    <row r="276">
+      <c r="A276" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B271" s="26" t="inlineStr">
+      <c r="B276" s="28" t="inlineStr">
         <is>
           <t>refresh_req_i || refresh_drain_i</t>
         </is>
       </c>
-      <c r="C271" s="26" t="inlineStr">
+      <c r="C276" s="28" t="inlineStr">
         <is>
           <t>refresh branch</t>
         </is>
       </c>
-      <c r="D271" s="26" t="inlineStr">
+      <c r="D276" s="28" t="inlineStr">
         <is>
           <t>see refresh-branch K-map; never falls through while pending</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="26" t="n">
+    <row r="277">
+      <c r="A277" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B272" s="26" t="inlineStr">
+      <c r="B277" s="28" t="inlineStr">
         <is>
           <t>rd_col_f</t>
         </is>
       </c>
-      <c r="C272" s="26" t="inlineStr">
+      <c r="C277" s="28" t="inlineStr">
         <is>
           <t>RD/RDA row-hit</t>
         </is>
       </c>
-      <c r="D272" s="26" t="inlineStr">
+      <c r="D277" s="28" t="inlineStr">
         <is>
           <t>read priority over write</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="26" t="n">
+    <row r="278">
+      <c r="A278" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B273" s="26" t="inlineStr">
+      <c r="B278" s="28" t="inlineStr">
         <is>
           <t>wr_col_f</t>
         </is>
       </c>
-      <c r="C273" s="26" t="inlineStr">
+      <c r="C278" s="28" t="inlineStr">
         <is>
           <t>WR/WRA row-hit</t>
         </is>
       </c>
-      <c r="D273" s="26" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="26" t="n">
+      <c r="D278" s="28" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B274" s="26" t="inlineStr">
+      <c r="B279" s="28" t="inlineStr">
         <is>
           <t>rd_act_f</t>
         </is>
       </c>
-      <c r="C274" s="26" t="inlineStr">
+      <c r="C279" s="28" t="inlineStr">
         <is>
           <t>ACT for oldest pending read</t>
         </is>
       </c>
-      <c r="D274" s="26" t="inlineStr">
+      <c r="D279" s="28" t="inlineStr">
         <is>
           <t>bank-parallel</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="26" t="n">
+    <row r="280">
+      <c r="A280" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B275" s="26" t="inlineStr">
+      <c r="B280" s="28" t="inlineStr">
         <is>
           <t>wr_act_f</t>
         </is>
       </c>
-      <c r="C275" s="26" t="inlineStr">
+      <c r="C280" s="28" t="inlineStr">
         <is>
           <t>ACT for oldest pending write</t>
         </is>
       </c>
-      <c r="D275" s="26" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="26" t="n">
+      <c r="D280" s="28" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B276" s="26" t="inlineStr">
+      <c r="B281" s="28" t="inlineStr">
         <is>
           <t>rd_pre_f</t>
         </is>
       </c>
-      <c r="C276" s="26" t="inlineStr">
+      <c r="C281" s="28" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (read)</t>
         </is>
       </c>
-      <c r="D276" s="26" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="26" t="n">
+      <c r="D281" s="28" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B277" s="26" t="inlineStr">
+      <c r="B282" s="28" t="inlineStr">
         <is>
           <t>wr_pre_f</t>
         </is>
       </c>
-      <c r="C277" s="26" t="inlineStr">
+      <c r="C282" s="28" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (write)</t>
         </is>
       </c>
-      <c r="D277" s="26" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="15" t="inlineStr">
+      <c r="D282" s="28" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="inlineStr">
         <is>
           <t>r_rfc_cnt next-value</t>
         </is>
       </c>
-      <c r="D280" s="17" t="inlineStr">
+      <c r="D285" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (tRFC counter)</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="20" t="inlineStr">
+    <row r="286">
+      <c r="A286" s="19" t="inlineStr">
         <is>
           <t>w_rfc_busy = (r_rfc_cnt != 0). Load wins over decrement; blocks ACT picks and further REFs (drain REFs are tRFC-spaced).</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="25" t="inlineStr">
+    <row r="287">
+      <c r="A287" s="27" t="inlineStr">
         <is>
           <t>w_fire_out &amp;&amp; r_grant (REF fired)</t>
         </is>
       </c>
-      <c r="B282" s="25" t="inlineStr">
+      <c r="B287" s="27" t="inlineStr">
         <is>
           <t>r_rfc_cnt != 0</t>
         </is>
       </c>
-      <c r="C282" s="25" t="inlineStr">
+      <c r="C287" s="27" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="26" t="inlineStr">
+    <row r="288">
+      <c r="A288" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B283" s="26" t="inlineStr">
+      <c r="B288" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C283" s="26" t="inlineStr">
+      <c r="C288" s="28" t="inlineStr">
         <is>
           <t>t_rfc_i (load)</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="26" t="inlineStr">
+    <row r="289">
+      <c r="A289" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B284" s="26" t="inlineStr">
+      <c r="B289" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C284" s="26" t="inlineStr">
+      <c r="C289" s="28" t="inlineStr">
         <is>
           <t>r_rfc_cnt - 1</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="26" t="inlineStr">
+    <row r="290">
+      <c r="A290" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B285" s="26" t="inlineStr">
+      <c r="B290" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C285" s="26" t="inlineStr">
+      <c r="C290" s="28" t="inlineStr">
         <is>
           <t>0 (idle)</t>
         </is>
@@ -6060,7 +6171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6116,978 +6227,1000 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (0,1,1): closed row, tRP and tRC elapsed. Any 1 with row_valid=1 would re-ACT an open bank.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    tRP counting =&gt; row closed. The PRE edge loads tRP and clears row_valid together, so (row_valid=1, rp!=0) cannot occur.</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>bank_timer.sv:106 + :120-123</t>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (0,1,1): closed row, tRP and tRC elapsed. Any 1 with row_valid=1 would re-ACT an open bank.</t>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    tRP counting =&gt; row closed. The PRE edge loads tRP and clears row_valid together, so (row_valid=1, rp!=0) cannot occur.</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:106 + :120-123</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="21" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="B14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="22" t="n">
+      <c r="B15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="B16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>cells: 6 reachable, 2 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    !row_valid &amp; rp==0 &amp; rc==0</t>
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !row_valid &amp; rp==0 &amp; rc==0</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 2 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>safe_rd_o / safe_wr_o</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:135-136</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>safe_rd = safe_wr = r_row_valid &amp;&amp; (r_rcd == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>rows = row_valid/rcd==0   cols = ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0). ap_pending=1 must kill columns — the row is committed to auto-close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    tRCD counting =&gt; row open. The ACT edge loads tRCD and sets row_valid together, so (row_valid=0, rcd!=0) cannot occur.</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:96 + :116</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0). ap_pending=1 must kill columns — the row is committed to auto-close.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="B34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B35" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="C35" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>cells: 6 reachable, 2 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    row_valid &amp; rcd==0 &amp; !ap_pending</t>
-        </is>
+      <c r="B36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: row_valid &amp; rcd==0 &amp; !ap_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 2 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>safe_pre_o</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:138</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>safe_pre = r_row_valid &amp;&amp; (r_ras == 0) &amp;&amp; (r_preblk == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>rows = row_valid/ras==0   cols = preblk==0/ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0): tRAS AND tRTP/tWR both elapsed, no auto-PRE in flight. preblk covers the read-to-PRE / write-recovery window the arbiter cannot see per-command.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    tRAS counting =&gt; row open. tRAS loads on the ACT edge that sets row_valid, so (row_valid=0, ras!=0) cannot occur.</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv (set_act_i -&gt; r_ras) + :116</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0): tRAS AND tRTP/tWR both elapsed, no auto-PRE in flight. preblk covers the read-to-PRE / write-recovery window the arbiter cannot see per-command.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E47" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="D51" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="22" t="n">
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>cells: 12 reachable, 4 don't-care (X) of 16. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    row_valid &amp; ras==0 &amp; preblk==0 &amp; !ap_pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+      <c r="B55" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: row_valid &amp; ras==0 &amp; preblk==0 &amp; !ap_pending</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>w_ap_fire (internal auto-precharge)</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:88</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t>w_ap_fire = r_ap_pending &amp;&amp; (r_preblk == 0) &amp;&amp; (r_ras == 0)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>rows = ap_pending/preblk==0   cols = ras==0</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) ap_pending is set by an AP column while the two timers run from the ACT and column edges, so a pending auto-precharge can sit through any combination of them. That is the flag's purpose.</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:88 + :115-127</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B67" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="22" t="n">
+      <c r="B73" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="21" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B69" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ap_pending &amp; preblk==0 &amp; ras==0</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="15" t="inlineStr">
-        <is>
-          <t>state_o (observability only)</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>bank_timer.sv:144-147</t>
-        </is>
+      <c r="B74" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: ap_pending &amp; preblk==0 &amp; ras==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>state_o (observability only)</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>bank_timer.sv:144-147</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
           <t>rv ? (rcd_nz ? ACTIVATING : ACTIVE) : (rp_nz ? PRECHARGING : IDLE)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>rows = row_valid/rcd_nz   cols = rp_nz</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Pure decode of the flags; no downstream logic may depend on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    rcd_nz =&gt; row_valid. The ACT edge loads tRCD and sets row_valid together, and nothing else loads tRCD, so a bank counting tRCD always has its row marked open.</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:96 (set_act_i -&gt; r_rcd) + :116 (r_row_valid &lt;= 1)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    rp_nz =&gt; !row_valid. The PRE edge (explicit or auto) loads tRP and clears row_valid together.</t>
         </is>
       </c>
-      <c r="D80" s="17" t="inlineStr">
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:106 (set_pre_i||w_ap_fire -&gt; r_rp) + :120-123 (r_row_valid &lt;= 0)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Therefore rcd_nz and rp_nz are MUTUALLY EXCLUSIVE -- a bank cannot be inside tRCD and tRP at once. That single relation removes a quarter of this grid; drawing 0s there would assert the decode had been checked in a state the timers forbid.</t>
         </is>
       </c>
-      <c r="D81" s="17" t="inlineStr">
+      <c r="D87" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:96,106,116,120-123</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Pure decode of the flags; no downstream logic may depend on it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B85" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C86" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B87" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>PRECHG</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C92" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>ACTIVATING</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B88" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="24" t="inlineStr">
+      <c r="B94" s="23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="C94" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>cells: 4 reachable, 4 don't-care (X) of 8. Read the CHECK over the reachable cells only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
         <is>
           <t>row_valid / ap_pending next-state priority</t>
         </is>
       </c>
-      <c r="D95" s="17" t="inlineStr">
+      <c r="D97" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:115-127</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="20" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>Strict priority ACT &gt; PRE &gt; auto-PRE &gt; column. The arbiter never issues ACT and PRE to one bank in one cycle (single-issue), so rows 1-2 cannot conflict in practice.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="25" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="27" t="inlineStr">
         <is>
           <t>set_act</t>
         </is>
       </c>
-      <c r="B97" s="25" t="inlineStr">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>set_pre</t>
         </is>
       </c>
-      <c r="C97" s="25" t="inlineStr">
+      <c r="C99" s="27" t="inlineStr">
         <is>
           <t>w_ap_fire</t>
         </is>
       </c>
-      <c r="D97" s="25" t="inlineStr">
+      <c r="D99" s="27" t="inlineStr">
         <is>
           <t>set_rd||set_wr</t>
         </is>
       </c>
-      <c r="E97" s="25" t="inlineStr">
+      <c r="E99" s="27" t="inlineStr">
         <is>
           <t>row_valid'</t>
         </is>
       </c>
-      <c r="F97" s="25" t="inlineStr">
+      <c r="F99" s="27" t="inlineStr">
         <is>
           <t>ap_pending'</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B98" s="26" t="inlineStr">
+      <c r="B100" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C98" s="26" t="inlineStr">
+      <c r="C100" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D98" s="26" t="inlineStr">
+      <c r="D100" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E98" s="26" t="inlineStr">
+      <c r="E100" s="28" t="inlineStr">
         <is>
           <t>1 (row=row_i)</t>
         </is>
       </c>
-      <c r="F98" s="26" t="inlineStr">
+      <c r="F100" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B99" s="26" t="inlineStr">
+      <c r="B101" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C99" s="26" t="inlineStr">
+      <c r="C101" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D99" s="26" t="inlineStr">
+      <c r="D101" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E99" s="26" t="inlineStr">
+      <c r="E101" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F99" s="26" t="inlineStr">
+      <c r="F101" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B100" s="26" t="inlineStr">
+      <c r="B102" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C100" s="26" t="inlineStr">
+      <c r="C102" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D100" s="26" t="inlineStr">
+      <c r="D102" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E100" s="26" t="inlineStr">
+      <c r="E102" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F100" s="26" t="inlineStr">
+      <c r="F102" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="26" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B101" s="26" t="inlineStr">
+      <c r="B103" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C101" s="26" t="inlineStr">
+      <c r="C103" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D101" s="26" t="inlineStr">
+      <c r="D103" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E101" s="26" t="inlineStr">
+      <c r="E103" s="28" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F101" s="26" t="inlineStr">
+      <c r="F103" s="28" t="inlineStr">
         <is>
           <t>set_ap_i</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="26" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B102" s="26" t="inlineStr">
+      <c r="B104" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C102" s="26" t="inlineStr">
+      <c r="C104" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D102" s="26" t="inlineStr">
+      <c r="D104" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E102" s="26" t="inlineStr">
+      <c r="E104" s="28" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F102" s="26" t="inlineStr">
+      <c r="F104" s="28" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
@@ -8605,7 +8738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8661,506 +8794,527 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a grant with nothing pending is swallowed (the accumulator never goes negative).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (independent) grant does NOT imply pend_nz. An EARLY grant -- the scheduler pulsing while pending is zero -- is an explicitly handled case (w_grant_early), so the (1,0) cell is reachable and must read 0, not X. Checked, and genuinely independent.</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>refresh_ctrl.sv:133-134</t>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): a grant with nothing pending is swallowed (the accumulator never goes negative).</t>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) grant does NOT imply pend_nz. An EARLY grant -- the scheduler pulsing while pending is zero -- is an explicitly handled case (w_grant_early), so the (1,0) cell is reachable and must read 0, not X. Checked, and genuinely independent.</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>refresh_ctrl.sv:133-134</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="21" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="B14" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="B15" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    grant &amp; pend_nz</t>
-        </is>
+      <c r="B17" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: grant &amp; pend_nz</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>refresh_drain_active</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:126</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>w_drain_active = (r_burst_remaining &gt; 0) &amp;&amp; (r_pending &gt; 0) &amp;&amp; refresh_req_o</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>rows = rem_nz/pend_nz   cols = req_o</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): holding the arbiter in the refresh branch requires quota AND owed refreshes AND the REGISTERED request. The req_o term is not redundant -- a postponed backlog withholds req_o while pending is non-zero, and without this term the drain window would open anyway and defeat the postpone credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) req_o does NOT follow pend_nz: a postponed backlog withholds the registered request while pending is non-zero. That is exactly why the term is in the equation, so all combinations occur.</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:186-192</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): holding the arbiter in the refresh branch requires quota AND owed refreshes AND the REGISTERED request. The req_o term is not redundant -- a postponed backlog withholds req_o while pending is non-zero, and without this term the drain window would open anyway and defeat the postpone credit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="B32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="B33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="22" t="n">
+      <c r="B34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    rem_nz &amp; pend_nz &amp; req_o</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+      <c r="B35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: rem_nz &amp; pend_nz &amp; req_o</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>r_pending next-value</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:98-108</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>refresh_req_o (registered) = pending&gt;0. Saturation at 8 = a JEDEC retention violation looming — the arbiter must be serving REFs.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>enable &amp;&amp; expired</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B42" s="27" t="inlineStr">
         <is>
           <t>w_grant_accept</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C43" s="28" t="inlineStr">
         <is>
           <t>min(pending+1, 8)  (postpone cap)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>pending-1</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>pending (net zero)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B46" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C46" s="28" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>busy_o</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>pumice_mem_cmd_scheduler.sv</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>busy = !init_done || refresh_req || w_cmd_rd_valid || (|w_bank_row_active[0])</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>rows = init_done/refresh_req   cols = cmd_rd_valid/any_row_active</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
-        <is>
-          <t>RELATIONS between axis signals (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at (1,0,0,0): init complete, no refresh owed, cmd FIFO empty, all rows closed. 15 of 16 cells are 1 — busy is the OR-reduce of everything in flight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) cmd_rd_valid is the command FIFO's read-valid and is not gated on init_done, and any_row_active is a registered image, so all sixteen combinations are reachable.</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>pumice_mem_cmd_scheduler.sv:527,574</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at (1,0,0,0): init complete, no refresh owed, cmd FIFO empty, all rows closed. 15 of 16 cells are 1 — busy is the OR-reduce of everything in flight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D54" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E54" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="21" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="22" t="n">
-        <v>1</v>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>pumice_mem_cmd_scheduler.sv:529,576</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B56" s="22" t="n">
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="22" t="n">
+      <c r="C59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="22" t="n">
+      <c r="D59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="22" t="n">
+      <c r="E59" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B57" s="22" t="n">
+      <c r="B61" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="22" t="n">
+      <c r="C61" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D57" s="22" t="n">
+      <c r="D61" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="22" t="n">
+      <c r="E61" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="21" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B58" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="22" t="n">
+      <c r="B62" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D58" s="22" t="n">
+      <c r="D62" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="22" t="n">
+      <c r="E62" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="19" t="inlineStr">
-        <is>
-          <t>IMPLICANTS (derived from the cells above, don't-cares used where they help):</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    any_row_active  |  cmd_rd_valid  |  refresh_req  |  !init_done</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compare against the documented equation above. A difference means the grid and the RTL expression disagree -- one of them is wrong, and the cells are computed, so it is the equation.</t>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !init_done  |  any_row_active  |  cmd_rd_valid  |  refresh_req</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10839,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>read 571.3 MB/s at ring 64 = write parity (570.2) and 95% of peak. Timing improved (+0.285 vs +0.039 ns). PUMICE-025.</t>
+          <t>read 571.3 MB/s at ring 64 = write parity (570.2) and 95% of peak. Timing improved (+0.285 vs +0.039 ns). pumice BUG-011 (was PUMICE-025).</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11621,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>idle/timeout close (fixed_open/adapt_time)</t>
+          <t>idle/timeout close (fixed_open)</t>
         </is>
       </c>
     </row>

--- a/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
+++ b/projects/components/memory-controllers/pumice-ddr2-lpddr2/docs/pumice_signal_contracts.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,12 +75,20 @@
       <i val="1"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="009C6500"/>
     </font>
     <font>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -153,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -203,7 +211,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -213,10 +220,17 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2729,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2925,9 +2939,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: The refresh pick is a WHOLE-CONTROLLER decision, so the axes are the only state that can block it: nothing in flight (any_active, inflight_preact), no bank guarded (guards_nz folds r_guard0|r_guard1 across all banks), tRFC not running, and no grant already outstanding. Per-bank identity is deliberately absent -- REFab touches every bank, so there is no bank to be selective about, and that is why the guard vectors are reduced to a single OR here.</t>
         </is>
       </c>
     </row>
@@ -2939,100 +2953,100 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="24" t="n">
+      <c r="C22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B23" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="24" t="n">
+      <c r="B23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="24" t="n">
+      <c r="B24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="24" t="n">
+      <c r="B25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3044,100 +3058,100 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="24" t="n">
+      <c r="B29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="24" t="n">
+      <c r="B30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="24" t="n">
+      <c r="B31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B32" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="24" t="n">
+      <c r="B32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3149,3012 +3163,3061 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      !any_active &amp; !inflight_preact &amp; !guards_nz &amp; !rfc_busy &amp; !grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>refresh-branch action (given refresh_req_i||refresh_drain_i)</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (priority 2)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>if (any_active) { if (rfsh_pre_found) PRE else wait } else if (ref_safe) REF else wait</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>rows = any_active/rfsh_pre_found   cols = ref_safe</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: REF appears ONLY where any_active=0 AND ref_safe=1. PRE only where any_active=1 AND pre_found=1. Everything else waits (the branch never falls through to column/ACT picks).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>cite</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>any_active</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>|r_bank_row_active[RK0]</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:1052</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>rfsh_pre_found</t>
+          <t>any_active</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>any j with r_bank_row_active[j] &amp;&amp; r_bank_pre_ready[j] &amp;&amp; !w_guarded[j]</t>
+          <t>|r_bank_row_active[RK0]</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv:1054-1058</t>
+          <t>pumice_cmd_arbiter.sv:1052</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
+          <t>rfsh_pre_found</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>any j with r_bank_row_active[j] &amp;&amp; r_bank_pre_ready[j] &amp;&amp; !w_guarded[j]</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:1054-1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
           <t>ref_safe</t>
         </is>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>w_ref_safe -- see its own map above</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (refresh pick gate)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ref_safe =&gt; !any_active. w_ref_safe is literally ANDed with !w_any_active, so the two cannot both be 1 -- half this grid cannot occur.</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (w_ref_safe = !w_any_active &amp;&amp; ...)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ref_safe =&gt; !any_active. w_ref_safe is literally ANDed with !w_any_active, so the two cannot both be 1 -- half this grid cannot occur.</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (w_ref_safe = !w_any_active &amp;&amp; ...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">    rfsh_pre_found =&gt; any_active. The search only sets it for a bank with r_bank_row_active[j] high, so 'a bank to precharge exists' implies 'a row is open'.</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:1054-1058</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="22" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Given the refresh request, the branch reads only whether work is in flight, whether a precharge is needed first, and whether the whole-controller safety gate is clear. The request itself is the map's precondition, not an axis; per-bank state is folded into rfsh_pre_found (a PRE is needed somewhere) and into ref_safe (map 1), which is why neither bank index nor timer values appear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C52" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>wait</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>REF</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B53" s="25" t="inlineStr">
+      <c r="B54" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C53" s="25" t="inlineStr">
+      <c r="C54" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B55" s="22" t="inlineStr">
         <is>
           <t>PRE</t>
         </is>
       </c>
-      <c r="C54" s="25" t="inlineStr">
+      <c r="C55" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B55" s="24" t="inlineStr">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>wait</t>
         </is>
       </c>
-      <c r="C55" s="25" t="inlineStr">
+      <c r="C56" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>rd_col_m[e]  (given rd_sch_valid_i[e] &amp;&amp; rd_issue_ready)</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>rd_col_m[e] = rhit &amp;&amp; r_bank_rdwr_ready[rb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; twtr_ok_i &amp;&amp; rd_issue_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [rd_issue_ready_i factored out as the enabling condition; dbl_issue = (f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]; col_guard = r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]]</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>rows = rhit/rdwr_ready   cols = tccd_ok/twtr_ok   pages = dbl_issue/col_guard</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the page [dbl_issue=0, col_guard=0], single all-ones cell. A 1 anywhere on a col_guard=1 page would mean a RD issued through a turnaround/AP/precharge guard -- the class that produced the 471/471 concurrent-soak corruption (a RD into a write burst's DQ occupancy on a stale flopped twtr_ok).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>cite</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>rhit</t>
-        </is>
-      </c>
-      <c r="B64" s="18" t="inlineStr">
-        <is>
-          <t>r_bank_row_active[RK0][rb] &amp;&amp; (row == r_bank_open_row[RK0][rb])</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv:562-563</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t>rdwr_ready</t>
+          <t>rhit</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>r_bank_rdwr_ready[RK0][rb] = safe_rd_o = r_row_valid &amp;&amp; (r_rcd=='0) &amp;&amp; !r_ap_pending</t>
+          <t>r_bank_row_active[RK0][rb] &amp;&amp; (row == r_bank_open_row[RK0][rb])</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
         <is>
-          <t>bank_timer.sv:135</t>
+          <t>pumice_cmd_arbiter.sv:562-563</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>tccd_ok</t>
+          <t>rdwr_ready</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>w_tccd_fwd_ok -- FORWARD tCCD at classify time, not the flopped tccd_ok_i</t>
+          <t>r_bank_rdwr_ready[RK0][rb] = safe_rd_o = r_row_valid &amp;&amp; (r_rcd=='0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv:420-432</t>
+          <t>bank_timer.sv:135</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>twtr_ok</t>
+          <t>tccd_ok</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>twtr_ok_i -- write-to-read turnaround, from global_timers</t>
+          <t>w_tccd_fwd_ok -- FORWARD tCCD at classify time, not the flopped tccd_ok_i</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
         <is>
-          <t>global_timers.sv</t>
+          <t>pumice_cmd_arbiter.sv:420-432</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>dbl_issue</t>
+          <t>twtr_ok</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>(f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]</t>
+          <t>twtr_ok_i -- write-to-read turnaround, from global_timers</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>pumice_cmd_arbiter.sv:361-371,383-385</t>
+          <t>global_timers.sv</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="inlineStr">
         <is>
+          <t>dbl_issue</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>(f_ap(rb) &amp;&amp; w_col_inflight_bank[rb]) | w_rd_col_inflight_ent[e]</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv:361-371,383-385</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
           <t>col_guard</t>
         </is>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>r_ap_closing[rb] | w_ref_col_block[rb] | w_rd_turn_block | w_ap_col_guard[rb] | w_pre_col_guard[rb] | w_preact_bank_guard[rb]</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:574-580</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="16" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) rhit and rdwr_ready both require an open row but neither implies the other: a hit can be pending tRCD (rdwr_ready=0), and a ready bank can hold the WRONG row (rhit=0). All four occur.</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:562-565 + bank_timer.sv:135</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Entry validity and rd_issue_ready are the precondition, so they are not axes. Everything else the column decision reads is on an axis, with two deliberate folds named in the expression: dbl_issue collapses the two double-issue sources (same-bank AP in flight, same-entry column in flight) and col_guard collapses the six per-bank column blockers. The entry index e and bank rb do not appear because every term is already evaluated for THIS entry's bank -- the map is one entry's slice, and the fold is where the bank-specific part lives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="22" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C75" s="22" t="inlineStr">
+      <c r="C76" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D75" s="22" t="inlineStr">
+      <c r="D76" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E75" s="22" t="inlineStr">
+      <c r="E76" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="22" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B76" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="22" t="inlineStr">
+      <c r="B77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B77" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="22" t="inlineStr">
+      <c r="B78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B78" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="23" t="n">
+      <c r="B79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="22" t="inlineStr">
+      <c r="E79" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B79" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="B80" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="22" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C82" s="22" t="inlineStr">
+      <c r="C83" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D82" s="22" t="inlineStr">
+      <c r="D83" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E82" s="22" t="inlineStr">
+      <c r="E83" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="22" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="22" t="inlineStr">
+      <c r="B84" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="22" t="inlineStr">
+      <c r="B85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="22" t="inlineStr">
+      <c r="B86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="B87" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="22" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C89" s="22" t="inlineStr">
+      <c r="C90" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D89" s="22" t="inlineStr">
+      <c r="D90" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E89" s="22" t="inlineStr">
+      <c r="E90" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="22" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="22" t="inlineStr">
+      <c r="B91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="22" t="inlineStr">
+      <c r="B92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="22" t="inlineStr">
+      <c r="B93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="B94" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="22" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C96" s="22" t="inlineStr">
+      <c r="C97" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D96" s="22" t="inlineStr">
+      <c r="D97" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E96" s="22" t="inlineStr">
+      <c r="E97" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="22" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B97" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="22" t="inlineStr">
+      <c r="B98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B98" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="22" t="inlineStr">
+      <c r="B99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B99" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="22" t="inlineStr">
+      <c r="B100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B100" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="18" t="inlineStr">
+      <c r="B101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: rhit &amp; rdwr_ready &amp; tccd_ok &amp; twtr_ok &amp; !dbl_issue &amp; !col_guard</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      rhit &amp; rdwr_ready &amp; tccd_ok &amp; twtr_ok &amp; !dbl_issue &amp; !col_guard</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="15" t="inlineStr">
+      <c r="A105" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="inlineStr">
         <is>
           <t>wr_col_m[e]  (given wr_sch_valid_i[e] &amp;&amp; wr_commit_ready)</t>
         </is>
       </c>
-      <c r="D105" s="17" t="inlineStr">
+      <c r="D107" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + direction guard)</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="18" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
         <is>
           <t>wr_col_m[e] = whit &amp;&amp; r_bank_rdwr_ready[wb] &amp;&amp; w_tccd_fwd_ok &amp;&amp; trtw_ok_i &amp;&amp; wr_commit_ready_i &amp;&amp; !dbl_issue &amp;&amp; !col_guard   [wr_commit_ready_i factored out; dbl_issue = (f_ap(wb) &amp;&amp; w_col_inflight_bank[wb]) | w_wr_col_inflight_ent[e]; col_guard = r_ap_closing[wb] | w_ref_col_block[wb] | w_wr_turn_block | w_ap_col_guard[wb] | w_pre_col_guard[wb] | w_preact_bank_guard[wb]]</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>rows = whit/rdwr_ready   cols = tccd_ok/trtw_ok   pages = dbl_issue/col_guard</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="19" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Exact mirror of rd_col_m with the write-side turnaround (trtw) and commit-ready: 1s only on [dbl_issue=0, col_guard=0].</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="21" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="16" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) dbl_issue and col_guard are independent: the first is double-issue prevention for THIS entry/bank, the second folds turnaround, AP and precharge guards. Either can hold alone.</t>
         </is>
       </c>
-      <c r="D111" s="17" t="inlineStr">
+      <c r="D113" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:581-587</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="A114" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: The read map's argument, mirrored: entry validity and wr_commit_ready are the precondition; dbl_issue and col_guard fold the same two families for the write bank wb; the turnaround axis is trtw_ok rather than twtr_ok because a write following a read is the opposite crossing. Nothing outside these can block a write column, which is what makes the six axes sufficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="B115" s="22" t="inlineStr">
+    <row r="117">
+      <c r="B117" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C115" s="22" t="inlineStr">
+      <c r="C117" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D115" s="22" t="inlineStr">
+      <c r="D117" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E115" s="22" t="inlineStr">
+      <c r="E117" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="22" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B116" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="22" t="inlineStr">
+      <c r="B118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B117" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="22" t="inlineStr">
+      <c r="B119" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B118" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C118" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="23" t="n">
+      <c r="B120" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="22" t="inlineStr">
+      <c r="E120" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B119" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
+      <c r="B121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=0, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" s="22" t="inlineStr">
+    <row r="124">
+      <c r="B124" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C122" s="22" t="inlineStr">
+      <c r="C124" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D122" s="22" t="inlineStr">
+      <c r="D124" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E122" s="22" t="inlineStr">
+      <c r="E124" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="22" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B123" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="22" t="inlineStr">
+      <c r="B125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B124" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="22" t="inlineStr">
+      <c r="B126" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B125" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="22" t="inlineStr">
+      <c r="B127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B126" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="B128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=0]</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="22" t="inlineStr">
+    <row r="131">
+      <c r="B131" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C129" s="22" t="inlineStr">
+      <c r="C131" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D129" s="22" t="inlineStr">
+      <c r="D131" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E129" s="22" t="inlineStr">
+      <c r="E131" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="22" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B130" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="22" t="inlineStr">
+      <c r="B132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B131" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="22" t="inlineStr">
+      <c r="B133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B132" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="22" t="inlineStr">
+      <c r="B134" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B133" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="B135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>[dbl_issue=1, col_guard=1]</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="B136" s="22" t="inlineStr">
+    <row r="138">
+      <c r="B138" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C136" s="22" t="inlineStr">
+      <c r="C138" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D136" s="22" t="inlineStr">
+      <c r="D138" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E136" s="22" t="inlineStr">
+      <c r="E138" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="22" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B137" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="22" t="inlineStr">
+      <c r="B139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B138" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="22" t="inlineStr">
+      <c r="B140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B139" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="22" t="inlineStr">
+      <c r="B141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B140" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="18" t="inlineStr">
+      <c r="B142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: whit &amp; rdwr_ready &amp; tccd_ok &amp; trtw_ok &amp; !dbl_issue &amp; !col_guard</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
     <row r="145">
-      <c r="A145" s="15" t="inlineStr">
+      <c r="A145" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      whit &amp; rdwr_ready &amp; tccd_ok &amp; trtw_ok &amp; !dbl_issue &amp; !col_guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="inlineStr">
         <is>
           <t>w_rd_turn_block / w_wr_turn_block</t>
         </is>
       </c>
-      <c r="D145" s="17" t="inlineStr">
+      <c r="D148" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (direction-turnaround guard)</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="18" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="18" t="inlineStr">
         <is>
           <t>w_rd_turn_block = r_wrfire0 || r_wrfire1 ; w_wr_turn_block = r_rdfire0 || r_rdfire1   (fire-shift of the OPPOSITE direction; covers the 2 cycles until the flopped twtr/trtw ok reflects the fired column)</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = oppfire0/oppfire1   cols = </t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="19" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Zero ONLY at (0,0). The guard is direction-CROSSED: a fired WR blocks RD picks and vice versa; same-direction pacing stays with tCCD. If either 1-cell reads 0, the turnaround hole is back.</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="21" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="20" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="16" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) The two fire flags are consecutive pipeline stages of the same event, so all four combinations occur as a fired column walks through: 01 means 'fired last cycle', 11 'two back to back'.</t>
         </is>
       </c>
-      <c r="D151" s="17" t="inlineStr">
+      <c r="D154" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (r_wrfire0/r_wrfire1)</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="22" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: A pure function of the OPPOSITE direction's two-deep fire shift and nothing else. It exists precisely because the flopped twtr/trtw ok bits lag the column they describe by two cycles, so no timer value belongs on an axis -- the shift register IS the state, and the map's point is that the block depends on nothing further.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="22" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B155" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="22" t="inlineStr">
+      <c r="B158" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B156" s="23" t="n">
+      <c r="B159" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="22" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B157" s="23" t="n">
+      <c r="B160" s="22" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B158" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="18" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: oppfire1  |  oppfire0</t>
-        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="21" t="inlineStr">
         <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B161" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="15" t="inlineStr">
+      <c r="A163" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: oppfire1  |  oppfire0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      oppfire0 | oppfire1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="inlineStr">
         <is>
           <t>rd_act_m[e] / wr_act_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D163" s="17" t="inlineStr">
+      <c r="D167" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify + tRFC gate)</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="18" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
         <is>
           <t>rd_act_m[e] = !r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; r_bank_act_ready[rb] &amp;&amp; w_act_classify_gate &amp;&amp; !w_rfc_busy   [w_act_classify_gate folds tfaw_ok_i &amp;&amp; trrd_ok_i; r_bank_act_ready samples the ADVISORY lookahead twin (bank_act_ready_la_i), the live set being enforced at the final stage -- see w_out_ready. wr_act_m[e] is the same with wb for rb]</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = act_ready/tfaw_ok   pages = trrd_ok/rfc_busy</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="19" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="21" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the page [trrd_ok=1, rfc_busy=0], single cell (row_active=0, guarded=0, act_ready=1, tfaw_ok=1). ANY 1 on an rfc_busy=1 page = ACT during refresh recovery — the silicon row-corruption bug the tRFC counter closes. VERDICT DIFFERS IS EXPECTED AND THE TERM STAYS: the derived cover drops !row_active because the relation below proves act_ready already implies it (safe_act_o is ANDed with !r_row_valid, bank_timer.sv:133), so half the grid is unreachable and the literal is free. The arbiter re-states it rather than relying on another module's internal invariant -- if bank_timer ever reported ready with a row open, this AND is what still blocks the ACT. Redundant by derivation, deliberate by design; not a defect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="20" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="16" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    act_ready =&gt; !row_active. bank_act_ready is safe_act_o, which is ANDed with !r_row_valid -- a bank with a row open never reports itself ready to activate. Half the grid cannot occur.</t>
         </is>
       </c>
-      <c r="D169" s="17" t="inlineStr">
+      <c r="D173" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:133 (safe_act_o = !r_row_valid &amp;&amp; ...)</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="8" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Entry validity is the precondition. The activation decision reads the bank's own row/guard/ready state plus the two global JEDEC windows, and w_act_classify_gate is split back onto its two axes (tfaw_ok, trrd_ok) so the fold cannot hide one of them. Note act_ready here is the ADVISORY lookahead twin: the live bank readiness is enforced later at the output register (map 9), which is why this map can be sufficient without a live timer axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=0, rfc_busy=0]</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="B173" s="22" t="inlineStr">
+    <row r="177">
+      <c r="B177" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C173" s="22" t="inlineStr">
+      <c r="C177" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D173" s="22" t="inlineStr">
+      <c r="D177" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E173" s="22" t="inlineStr">
+      <c r="E177" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="22" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B174" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="22" t="inlineStr">
+      <c r="B178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B175" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C175" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="22" t="inlineStr">
+      <c r="B179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B176" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" s="25" t="inlineStr">
+      <c r="B180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E176" s="25" t="inlineStr">
+      <c r="E180" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="22" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B177" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" s="25" t="inlineStr">
+      <c r="B181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E177" s="25" t="inlineStr">
+      <c r="E181" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=0, rfc_busy=1]</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="B180" s="22" t="inlineStr">
+    <row r="184">
+      <c r="B184" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C180" s="22" t="inlineStr">
+      <c r="C184" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D180" s="22" t="inlineStr">
+      <c r="D184" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E180" s="22" t="inlineStr">
+      <c r="E184" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="22" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B181" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C181" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="22" t="inlineStr">
+      <c r="B185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B182" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C182" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D182" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E182" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="22" t="inlineStr">
+      <c r="B186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B183" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C183" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D183" s="25" t="inlineStr">
+      <c r="B187" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E183" s="25" t="inlineStr">
+      <c r="E187" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="22" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B184" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C184" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" s="25" t="inlineStr">
+      <c r="B188" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E184" s="25" t="inlineStr">
+      <c r="E188" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="8" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=1, rfc_busy=0]</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="B187" s="22" t="inlineStr">
+    <row r="191">
+      <c r="B191" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C187" s="22" t="inlineStr">
+      <c r="C191" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D187" s="22" t="inlineStr">
+      <c r="D191" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E187" s="22" t="inlineStr">
+      <c r="E191" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="22" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B188" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C188" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D188" s="23" t="n">
+      <c r="B192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E188" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="22" t="inlineStr">
+      <c r="E192" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B189" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D189" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E189" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="22" t="inlineStr">
+      <c r="B193" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B190" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C190" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D190" s="25" t="inlineStr">
+      <c r="B194" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C194" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E190" s="25" t="inlineStr">
+      <c r="E194" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="22" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B191" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D191" s="25" t="inlineStr">
+      <c r="B195" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E191" s="25" t="inlineStr">
+      <c r="E195" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="8" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
         <is>
           <t>[trrd_ok=1, rfc_busy=1]</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="B194" s="22" t="inlineStr">
+    <row r="198">
+      <c r="B198" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C194" s="22" t="inlineStr">
+      <c r="C198" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr">
+      <c r="D198" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E194" s="22" t="inlineStr">
+      <c r="E198" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="22" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B195" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C195" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E195" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="22" t="inlineStr">
+      <c r="B199" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B196" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C196" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D196" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="22" t="inlineStr">
+      <c r="B200" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B197" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C197" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D197" s="25" t="inlineStr">
+      <c r="B201" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E197" s="25" t="inlineStr">
+      <c r="E201" s="25" t="inlineStr">
         <is>
           <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B198" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C198" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D198" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E198" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="18" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: !guarded &amp; act_ready &amp; tfaw_ok &amp; trrd_ok &amp; !rfc_busy</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (1 ones, 16 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="21" t="inlineStr">
         <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B202" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E202" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="15" t="inlineStr">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !guarded &amp; act_ready &amp; tfaw_ok &amp; trrd_ok &amp; !rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 16 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      !row_active &amp; !guarded &amp; act_ready &amp; tfaw_ok &amp; trrd_ok &amp; !rfc_busy</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="28" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="inlineStr">
         <is>
           <t>rd_pre_m[e] / wr_pre_m[e]  (given sch_valid[e])</t>
         </is>
       </c>
-      <c r="D204" s="17" t="inlineStr">
+      <c r="D209" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (classify)</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="18" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="18" t="inlineStr">
         <is>
           <t>rd_pre_m[e] = r_bank_row_active[rb] &amp;&amp; !w_guarded[rb] &amp;&amp; !rhit &amp;&amp; r_bank_pre_ready[rb]   [wr_pre_m[e] is the same with wb/whit]</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>rows = row_active/guarded   cols = hit/pre_ready</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="19" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="21" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="19" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0,0,1): only an open bank on the WRONG row, un-guarded and tRAS/tRTP/tWR-clear, may precharge. A 1 with guarded=1 = the registered-readiness staleness hazard. VERDICT DIFFERS IS EXPECTED AND THE TERM STAYS: the derived cover drops row_active because the relations below prove BOTH hit and pre_ready already imply it (safe_pre_o is ANDed with r_row_valid), leaving the literal free. It is kept for the same reason as the activate map: the arbiter does not lean on the bank timer's internal invariant to avoid precharging a closed bank. Redundant by derivation, deliberate by design; not a defect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="20" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="16" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    hit =&gt; row_active. A row HIT is defined as 'this bank has a row open AND it is the requested one', so a hit with no open row is not a state the hardware can be in -- it is a contradiction in the term itself, not a case the logic happens to avoid.</t>
         </is>
       </c>
-      <c r="D210" s="17" t="inlineStr">
+      <c r="D215" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:562-565 (rhit/whit = r_bank_row_active[b] &amp;&amp; row==open_row)</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="16" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    pre_ready =&gt; row_active. safe_pre_o is ANDed with r_row_valid, so tRAS/tRTP/tWR clearance is only ever reported for a bank that has a row to precharge.</t>
         </is>
       </c>
-      <c r="D211" s="17" t="inlineStr">
+      <c r="D216" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:138 (safe_pre_o = r_row_valid &amp;&amp; (r_ras=='0) &amp;&amp; (r_preblk=='0) &amp;&amp; !r_ap_pending)</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="B214" s="22" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Entry validity is the precondition. A precharge is decided entirely by this bank's row state, its guard, whether the request hits the open row, and the bank's PRE readiness -- no global window applies, since tRP and tRAS are enforced inside the bank timer and surface through pre_ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C214" s="22" t="inlineStr">
+      <c r="C219" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D214" s="22" t="inlineStr">
+      <c r="D219" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E214" s="22" t="inlineStr">
+      <c r="E219" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="22" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B215" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C215" s="25" t="inlineStr">
+      <c r="B220" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D215" s="25" t="inlineStr">
+      <c r="D220" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E215" s="25" t="inlineStr">
+      <c r="E220" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="22" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B216" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C216" s="25" t="inlineStr">
+      <c r="B221" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C221" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D216" s="25" t="inlineStr">
+      <c r="D221" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E216" s="25" t="inlineStr">
+      <c r="E221" s="25" t="inlineStr">
         <is>
           <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B217" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C217" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D217" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E217" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B218" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C218" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D218" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E218" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="18" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: !guarded &amp; !hit &amp; pre_ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (1 ones, 6 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="21" t="inlineStr">
         <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="15" t="inlineStr">
-        <is>
-          <t>w_guarded[b]</t>
-        </is>
-      </c>
-      <c r="D224" s="17" t="inlineStr">
-        <is>
-          <t>pumice_cmd_arbiter.sv (guard fold)</t>
-        </is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B222" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C222" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B223" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C223" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="18" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: !guarded &amp; !hit &amp; pre_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 6 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      row_active &amp; !guarded &amp; !hit &amp; pre_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="28" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="15" t="inlineStr">
+        <is>
+          <t>w_guarded[b]</t>
+        </is>
+      </c>
+      <c r="D230" s="17" t="inlineStr">
+        <is>
+          <t>pumice_cmd_arbiter.sv (guard fold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="18" t="inlineStr">
+        <is>
           <t>w_guarded[b] = r_guard0[b] | r_guard1[b] | w_prepick_guard[b] | w_col_inflight_guard[b] | w_if_preact_out[b] | w_if_col_out[b]   [guards_nz = w_prepick_guard[b] | w_col_inflight_guard[b]; bank_match = w_if_preact_out[b] | w_if_col_out[b], the in-flight shadow's OUT stage -- each is (inflight_class ? 1&lt;&lt;r_bank : 0), so their OR is the old ((preact||col) &amp;&amp; r_bank==b) term by construction]</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>rows = guard0/guard1   cols = pick_guards_nz/inflight_rowop_or_col   pages = bank_match</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="19" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Zero ONLY when both guard stages are clear AND no in-flight row-affecting/column op targets this bank. Columns are included (tRTP/tWR registration lag) — if the (0,0,1,1) cell ever reads 0, the column-guard extension was lost.</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="8" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="8" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B229" s="8" t="inlineStr">
+      <c r="B235" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D229" s="8" t="inlineStr">
+      <c r="D235" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="17" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="17" t="inlineStr">
         <is>
           <t>guard0</t>
         </is>
       </c>
-      <c r="B230" s="18" t="inlineStr">
+      <c r="B236" s="18" t="inlineStr">
         <is>
           <t>r_guard0[b] / r_guard1[b] -- the two registered guard stages a pick walks through</t>
         </is>
       </c>
-      <c r="D230" s="17" t="inlineStr">
+      <c r="D236" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="17" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="17" t="inlineStr">
         <is>
           <t>guard1</t>
         </is>
       </c>
-      <c r="B231" s="18" t="inlineStr">
+      <c r="B237" s="18" t="inlineStr">
         <is>
           <t>r_guard0[b] / r_guard1[b] -- the two registered guard stages a pick walks through</t>
         </is>
       </c>
-      <c r="D231" s="17" t="inlineStr">
+      <c r="D237" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="17" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="17" t="inlineStr">
         <is>
           <t>pick_guards_nz</t>
         </is>
       </c>
-      <c r="B232" s="18" t="inlineStr">
+      <c r="B238" s="18" t="inlineStr">
         <is>
           <t>w_prepick_guard[b] | w_col_inflight_guard[b]</t>
         </is>
       </c>
-      <c r="D232" s="17" t="inlineStr">
+      <c r="D238" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:346-350</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="17" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="17" t="inlineStr">
         <is>
           <t>inflight_rowop_or_col</t>
         </is>
       </c>
-      <c r="B233" s="18" t="inlineStr">
+      <c r="B239" s="18" t="inlineStr">
         <is>
           <t>w_inflight_preact || w_inflight_col</t>
         </is>
       </c>
-      <c r="D233" s="17" t="inlineStr">
+      <c r="D239" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv:300-302</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="17" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="17" t="inlineStr">
         <is>
           <t>bank_match</t>
         </is>
       </c>
-      <c r="B234" s="18" t="inlineStr">
+      <c r="B240" s="18" t="inlineStr">
         <is>
           <t>r_bank == b -- the in-flight pick targets THIS bank</t>
         </is>
       </c>
-      <c r="D234" s="17" t="inlineStr">
+      <c r="D240" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="20" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="16" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) The guard stages are a shift register, so guard0/guard1 take all four combinations as a pick moves through; bank_match is an address compare independent of all of them.</t>
         </is>
       </c>
-      <c r="D236" s="17" t="inlineStr">
+      <c r="D242" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (guard fold)</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="8" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: The guard fold for one bank is the OR of every source that can guard it, and the axes enumerate all of them: the two registered guard vectors, the pick-stage guards (pick_guards_nz folds prepick and column-inflight), and the in-flight shadow's OUT stage. bank_match is the OR of the two out-stage one-hots, each built as (inflight_class ? 1&lt;&lt;r_bank : 0), so their OR is the old ((preact||col) &amp;&amp; r_bank==b) term BY CONSTRUCTION -- which is why the bank index itself need not be an axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
         <is>
           <t>[bank_match=0]</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="B240" s="22" t="inlineStr">
+    <row r="246">
+      <c r="B246" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C240" s="22" t="inlineStr">
+      <c r="C246" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D240" s="22" t="inlineStr">
+      <c r="D246" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E240" s="22" t="inlineStr">
+      <c r="E246" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="22" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B241" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D241" s="23" t="n">
+      <c r="B247" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E241" s="23" t="n">
+      <c r="E247" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="22" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B242" s="23" t="n">
+      <c r="B248" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C242" s="23" t="n">
+      <c r="C248" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D242" s="23" t="n">
+      <c r="D248" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E242" s="23" t="n">
+      <c r="E248" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="22" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B243" s="23" t="n">
+      <c r="B249" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C243" s="23" t="n">
+      <c r="C249" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D243" s="23" t="n">
+      <c r="D249" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="23" t="n">
+      <c r="E249" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="22" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B244" s="23" t="n">
+      <c r="B250" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C244" s="23" t="n">
+      <c r="C250" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D244" s="23" t="n">
+      <c r="D250" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E244" s="23" t="n">
+      <c r="E250" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="8" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="8" t="inlineStr">
         <is>
           <t>[bank_match=1]</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="B247" s="22" t="inlineStr">
+    <row r="253">
+      <c r="B253" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C247" s="22" t="inlineStr">
+      <c r="C253" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D247" s="22" t="inlineStr">
+      <c r="D253" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E247" s="22" t="inlineStr">
+      <c r="E253" s="21" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="22" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B248" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C248" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D248" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="22" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B249" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C249" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D249" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E249" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B250" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C250" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D250" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E250" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B251" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C251" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D251" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E251" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="18" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: inflight_rowop_or_col &amp; bank_match  |  pick_guards_nz  |  guard1  |  guard0</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="21" t="inlineStr">
         <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B254" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C254" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D254" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B255" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="15" t="inlineStr">
+      <c r="A256" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B256" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C256" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B257" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: inflight_rowop_or_col &amp; bank_match  |  pick_guards_nz  |  guard1  |  guard0</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      guard0 | guard1 | pick_guards_nz | inflight_rowop_or_col &amp; bank_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="15" t="inlineStr">
         <is>
           <t>w_out_ready / w_fire_out</t>
         </is>
       </c>
-      <c r="D256" s="17" t="inlineStr">
+      <c r="D263" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (output register)</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="18" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="18" t="inlineStr">
         <is>
           <t>w_out_ready = !r_pick_valid || cmd_ready_i || w_out_reject ; w_fire_out = r_pick_valid &amp;&amp; cmd_ready_i &amp;&amp; w_out_safe   [w_out_safe = the LIVE bank readiness for the op in the output register; w_out_reject = r_pick_valid &amp;&amp; !w_out_safe. A rejected pick is DROPPED, not held -- holding freezes w_out_ready and head-of-line blocks the pipeline. cmd_ready is folded to (cmd_ready_i &amp;&amp; w_out_safe) for this map's axes]</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = pick_valid/cmd_ready   cols = </t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="19" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: hold ONLY at (1,0) — a full cmd FIFO holds the decision; fire ONLY at (1,1). Guards/commits/grants strobe on fire alone.</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="21" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="20" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="16" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) pick_valid is internal; cmd_ready_i belongs to the downstream FIFO. Nothing couples them, so all four occur -- which is what makes the pick pipeline latency rather than a rate limit.</t>
         </is>
       </c>
-      <c r="D262" s="17" t="inlineStr">
+      <c r="D269" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (output register)</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="B265" s="22" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: The output register's handshake depends only on whether a pick is held and whether the consumer can take it. The live safety re-check is folded INTO the cmd_ready axis (cmd_ready &amp;&amp; w_out_safe) rather than given its own axis, because a rejected pick is dropped rather than held -- so safety changes which of the two outcomes occurs, not whether the slot frees. That fold is the whole subtlety of this map and is stated in the expression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="22" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B266" s="23" t="inlineStr">
+      <c r="B273" s="22" t="inlineStr">
         <is>
           <t>rdy</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="22" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B267" s="23" t="inlineStr">
+      <c r="B274" s="22" t="inlineStr">
         <is>
           <t>rdy</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="22" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B268" s="23" t="inlineStr">
+      <c r="B275" s="22" t="inlineStr">
         <is>
           <t>rdy+fire</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="22" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B269" s="24" t="inlineStr">
+      <c r="B276" s="23" t="inlineStr">
         <is>
           <t>hold</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="15" t="inlineStr">
+    <row r="279">
+      <c r="A279" s="15" t="inlineStr">
         <is>
           <t>pick priority (strict, first match wins)</t>
         </is>
       </c>
-      <c r="D272" s="17" t="inlineStr">
+      <c r="D279" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (always_comb pick)</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="19" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="19" t="inlineStr">
         <is>
           <t>Strict if/else cascade — exactly one action per cycle; refresh starves columns by design while req is high (liveness relies on tREFI &gt;&gt; refresh service time).</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="27" t="inlineStr">
+    <row r="281">
+      <c r="A281" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B274" s="27" t="inlineStr">
+      <c r="B281" s="29" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C274" s="27" t="inlineStr">
+      <c r="C281" s="29" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="D274" s="27" t="inlineStr">
+      <c r="D281" s="29" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="28" t="n">
+    <row r="282">
+      <c r="A282" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B275" s="28" t="inlineStr">
+      <c r="B282" s="30" t="inlineStr">
         <is>
           <t>!init_done_i &amp;&amp; init_cmd_valid_i</t>
         </is>
       </c>
-      <c r="C275" s="28" t="inlineStr">
+      <c r="C282" s="30" t="inlineStr">
         <is>
           <t>forward init op</t>
         </is>
       </c>
-      <c r="D275" s="28" t="inlineStr">
+      <c r="D282" s="30" t="inlineStr">
         <is>
           <t>MRS/PRE/REF from init_sequencer verbatim</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="28" t="n">
+    <row r="283">
+      <c r="A283" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B276" s="28" t="inlineStr">
+      <c r="B283" s="30" t="inlineStr">
         <is>
           <t>refresh_req_i || refresh_drain_i</t>
         </is>
       </c>
-      <c r="C276" s="28" t="inlineStr">
+      <c r="C283" s="30" t="inlineStr">
         <is>
           <t>refresh branch</t>
         </is>
       </c>
-      <c r="D276" s="28" t="inlineStr">
+      <c r="D283" s="30" t="inlineStr">
         <is>
           <t>see refresh-branch K-map; never falls through while pending</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="28" t="n">
+    <row r="284">
+      <c r="A284" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B277" s="28" t="inlineStr">
+      <c r="B284" s="30" t="inlineStr">
         <is>
           <t>rd_col_f</t>
         </is>
       </c>
-      <c r="C277" s="28" t="inlineStr">
+      <c r="C284" s="30" t="inlineStr">
         <is>
           <t>RD/RDA row-hit</t>
         </is>
       </c>
-      <c r="D277" s="28" t="inlineStr">
+      <c r="D284" s="30" t="inlineStr">
         <is>
           <t>read priority over write</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="28" t="n">
+    <row r="285">
+      <c r="A285" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B278" s="28" t="inlineStr">
+      <c r="B285" s="30" t="inlineStr">
         <is>
           <t>wr_col_f</t>
         </is>
       </c>
-      <c r="C278" s="28" t="inlineStr">
+      <c r="C285" s="30" t="inlineStr">
         <is>
           <t>WR/WRA row-hit</t>
         </is>
       </c>
-      <c r="D278" s="28" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="28" t="n">
+      <c r="D285" s="30" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B279" s="28" t="inlineStr">
+      <c r="B286" s="30" t="inlineStr">
         <is>
           <t>rd_act_f</t>
         </is>
       </c>
-      <c r="C279" s="28" t="inlineStr">
+      <c r="C286" s="30" t="inlineStr">
         <is>
           <t>ACT for oldest pending read</t>
         </is>
       </c>
-      <c r="D279" s="28" t="inlineStr">
+      <c r="D286" s="30" t="inlineStr">
         <is>
           <t>bank-parallel</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="28" t="n">
+    <row r="287">
+      <c r="A287" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B280" s="28" t="inlineStr">
+      <c r="B287" s="30" t="inlineStr">
         <is>
           <t>wr_act_f</t>
         </is>
       </c>
-      <c r="C280" s="28" t="inlineStr">
+      <c r="C287" s="30" t="inlineStr">
         <is>
           <t>ACT for oldest pending write</t>
         </is>
       </c>
-      <c r="D280" s="28" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="28" t="n">
+      <c r="D287" s="30" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B281" s="28" t="inlineStr">
+      <c r="B288" s="30" t="inlineStr">
         <is>
           <t>rd_pre_f</t>
         </is>
       </c>
-      <c r="C281" s="28" t="inlineStr">
+      <c r="C288" s="30" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (read)</t>
         </is>
       </c>
-      <c r="D281" s="28" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="28" t="n">
+      <c r="D288" s="30" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B282" s="28" t="inlineStr">
+      <c r="B289" s="30" t="inlineStr">
         <is>
           <t>wr_pre_f</t>
         </is>
       </c>
-      <c r="C282" s="28" t="inlineStr">
+      <c r="C289" s="30" t="inlineStr">
         <is>
           <t>PRE wrong-row bank (write)</t>
         </is>
       </c>
-      <c r="D282" s="28" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="15" t="inlineStr">
+      <c r="D289" s="30" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="15" t="inlineStr">
         <is>
           <t>r_rfc_cnt next-value</t>
         </is>
       </c>
-      <c r="D285" s="17" t="inlineStr">
+      <c r="D292" s="17" t="inlineStr">
         <is>
           <t>pumice_cmd_arbiter.sv (tRFC counter)</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="19" t="inlineStr">
+    <row r="293">
+      <c r="A293" s="19" t="inlineStr">
         <is>
           <t>w_rfc_busy = (r_rfc_cnt != 0). Load wins over decrement; blocks ACT picks and further REFs (drain REFs are tRFC-spaced).</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="27" t="inlineStr">
+    <row r="294">
+      <c r="A294" s="29" t="inlineStr">
         <is>
           <t>w_fire_out &amp;&amp; r_grant (REF fired)</t>
         </is>
       </c>
-      <c r="B287" s="27" t="inlineStr">
+      <c r="B294" s="29" t="inlineStr">
         <is>
           <t>r_rfc_cnt != 0</t>
         </is>
       </c>
-      <c r="C287" s="27" t="inlineStr">
+      <c r="C294" s="29" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="28" t="inlineStr">
+    <row r="295">
+      <c r="A295" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B288" s="28" t="inlineStr">
+      <c r="B295" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C288" s="28" t="inlineStr">
+      <c r="C295" s="30" t="inlineStr">
         <is>
           <t>t_rfc_i (load)</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="28" t="inlineStr">
+    <row r="296">
+      <c r="A296" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B289" s="28" t="inlineStr">
+      <c r="B296" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C289" s="28" t="inlineStr">
+      <c r="C296" s="30" t="inlineStr">
         <is>
           <t>r_rfc_cnt - 1</t>
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="28" t="inlineStr">
+    <row r="297">
+      <c r="A297" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B290" s="28" t="inlineStr">
+      <c r="B297" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C290" s="28" t="inlineStr">
+      <c r="C297" s="30" t="inlineStr">
         <is>
           <t>0 (idle)</t>
         </is>
@@ -6171,7 +6234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6232,7 +6295,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
@@ -6258,65 +6321,65 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: One bank's activate safety is exactly: no row open, tRP elapsed, tRC elapsed. No other bank and no global window appears because tFAW and tRRD are enforced by the arbiter across banks (map 6), not by the per-bank timer -- the division of labour is what makes three axes sufficient here.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="24" t="n">
+      <c r="B14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="23" t="n">
+      <c r="B15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="24" t="n">
+      <c r="B16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -6340,887 +6403,915 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  (1 ones, 2 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      !row_valid &amp; rp==0 &amp; rc==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>safe_rd_o / safe_wr_o</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:135-136</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>safe_rd = safe_wr = r_row_valid &amp;&amp; (r_rcd == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>rows = row_valid/rcd==0   cols = ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0). ap_pending=1 must kill columns — the row is committed to auto-close.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    tRCD counting =&gt; row open. The ACT edge loads tRCD and sets row_valid together, so (row_valid=0, rcd!=0) cannot occur.</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:96 + :116</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="22" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: A column is safe exactly when the row is open, tRCD has elapsed, and no auto-precharge is pending on the bank. Reads and writes share one expression because the direction-dependent windows (tWTR, tRTW, tCCD) are global and live in the arbiter, not in the bank timer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C34" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n">
+      <c r="B36" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="C36" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B36" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="B37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: row_valid &amp; rcd==0 &amp; !ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="26" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  (1 ones, 2 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      row_valid &amp; rcd==0 &amp; !ap_pending</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>safe_pre_o</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:138</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>safe_pre = r_row_valid &amp;&amp; (r_ras == 0) &amp;&amp; (r_preblk == 0) &amp;&amp; !r_ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>rows = row_valid/ras==0   cols = preblk==0/ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0): tRAS AND tRTP/tWR both elapsed, no auto-PRE in flight. preblk covers the read-to-PRE / write-recovery window the arbiter cannot see per-command.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    tRAS counting =&gt; row open. tRAS loads on the ACT edge that sets row_valid, so (row_valid=0, ras!=0) cannot occur.</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv (set_act_i -&gt; r_ras) + :116</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
-      <c r="B51" s="22" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Precharge safety is the row being open, tRAS elapsed, the read-to-PRE / write-recovery window elapsed (preblk, which covers tRTP and tWR together), and no auto-precharge already committed. preblk is a single axis on purpose: the arbiter cannot see per-command which of tRTP or tWR applies, so the timer merges them and that merge is the axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C53" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D51" s="22" t="inlineStr">
+      <c r="D53" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E51" s="22" t="inlineStr">
+      <c r="E53" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B52" s="25" t="inlineStr">
+      <c r="B54" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C52" s="25" t="inlineStr">
+      <c r="C54" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D52" s="25" t="inlineStr">
+      <c r="D54" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E52" s="25" t="inlineStr">
+      <c r="E54" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="B55" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B54" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="23" t="n">
+      <c r="B56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B55" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="B57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: row_valid &amp; ras==0 &amp; preblk==0 &amp; !ap_pending</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  (1 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      row_valid &amp; ras==0 &amp; preblk==0 &amp; !ap_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>w_ap_fire (internal auto-precharge)</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:88</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>w_ap_fire = r_ap_pending &amp;&amp; (r_preblk == 0) &amp;&amp; (r_ras == 0)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>rows = ap_pending/preblk==0   cols = ras==0</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="19" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). Fires exactly once: it clears ap_pending and row_valid and loads tRP the same edge.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="21" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) ap_pending is set by an AP column while the two timers run from the ACT and column edges, so a pending auto-precharge can sit through any combination of them. That is the flag's purpose.</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:88 + :115-127</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="22" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: The internal auto-precharge fires on the bank's own committed flag plus the two windows that gate any precharge. row_valid is deliberately NOT an axis: ap_pending can only have been set by a column to an open row, so it implies row_valid, and adding it would introduce cells that cannot occur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C73" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="22" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B71" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="22" t="inlineStr">
+      <c r="B74" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B72" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="22" t="inlineStr">
+      <c r="B75" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B73" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="23" t="n">
+      <c r="B76" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="22" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B74" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="18" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: ap_pending &amp; preblk==0 &amp; ras==0</t>
-        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="15" t="inlineStr">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: ap_pending &amp; preblk==0 &amp; ras==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      ap_pending &amp; preblk==0 &amp; ras==0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
         <is>
           <t>state_o (observability only)</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:144-147</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="18" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
         <is>
           <t>rv ? (rcd_nz ? ACTIVATING : ACTIVE) : (rp_nz ? PRECHARGING : IDLE)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>rows = row_valid/rcd_nz   cols = rp_nz</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="19" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Pure decode of the flags; no downstream logic may depend on it.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="21" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    rcd_nz =&gt; row_valid. The ACT edge loads tRCD and sets row_valid together, and nothing else loads tRCD, so a bank counting tRCD always has its row marked open.</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:96 (set_act_i -&gt; r_rcd) + :116 (r_row_valid &lt;= 1)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    rp_nz =&gt; !row_valid. The PRE edge (explicit or auto) loads tRP and clears row_valid together.</t>
         </is>
       </c>
-      <c r="D86" s="17" t="inlineStr">
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:106 (set_pre_i||w_ap_fire -&gt; r_rp) + :120-123 (r_row_valid &lt;= 0)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Therefore rcd_nz and rp_nz are MUTUALLY EXCLUSIVE -- a bank cannot be inside tRCD and tRP at once. That single relation removes a quarter of this grid; drawing 0s there would assert the decode had been checked in a state the timers forbid.</t>
         </is>
       </c>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="D91" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:96,106,116,120-123</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="22" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: The reported state is a pure decode of the row-valid flag and whether the two transition timers are still counting. It is observability only -- nothing in the controller consumes it -- so no input that affects BEHAVIOUR belongs on an axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C90" s="22" t="inlineStr">
+      <c r="C94" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="22" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B91" s="24" t="inlineStr">
+      <c r="B95" s="23" t="inlineStr">
         <is>
           <t>IDLE</t>
         </is>
       </c>
-      <c r="C91" s="23" t="inlineStr">
+      <c r="C95" s="22" t="inlineStr">
         <is>
           <t>PRECHG</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="22" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B92" s="25" t="inlineStr">
+      <c r="B96" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C92" s="25" t="inlineStr">
+      <c r="C96" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="22" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B93" s="23" t="inlineStr">
+      <c r="B97" s="22" t="inlineStr">
         <is>
           <t>ACTIVATING</t>
         </is>
       </c>
-      <c r="C93" s="25" t="inlineStr">
+      <c r="C97" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="22" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B94" s="23" t="inlineStr">
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="C94" s="25" t="inlineStr">
+      <c r="C98" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="15" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
         <is>
           <t>row_valid / ap_pending next-state priority</t>
         </is>
       </c>
-      <c r="D97" s="17" t="inlineStr">
+      <c r="D101" s="17" t="inlineStr">
         <is>
           <t>bank_timer.sv:115-127</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="19" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr">
         <is>
           <t>Strict priority ACT &gt; PRE &gt; auto-PRE &gt; column. The arbiter never issues ACT and PRE to one bank in one cycle (single-issue), so rows 1-2 cannot conflict in practice.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="27" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="29" t="inlineStr">
         <is>
           <t>set_act</t>
         </is>
       </c>
-      <c r="B99" s="27" t="inlineStr">
+      <c r="B103" s="29" t="inlineStr">
         <is>
           <t>set_pre</t>
         </is>
       </c>
-      <c r="C99" s="27" t="inlineStr">
+      <c r="C103" s="29" t="inlineStr">
         <is>
           <t>w_ap_fire</t>
         </is>
       </c>
-      <c r="D99" s="27" t="inlineStr">
+      <c r="D103" s="29" t="inlineStr">
         <is>
           <t>set_rd||set_wr</t>
         </is>
       </c>
-      <c r="E99" s="27" t="inlineStr">
+      <c r="E103" s="29" t="inlineStr">
         <is>
           <t>row_valid'</t>
         </is>
       </c>
-      <c r="F99" s="27" t="inlineStr">
+      <c r="F103" s="29" t="inlineStr">
         <is>
           <t>ap_pending'</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="28" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B100" s="28" t="inlineStr">
+      <c r="B104" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C100" s="28" t="inlineStr">
+      <c r="C104" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D100" s="28" t="inlineStr">
+      <c r="D104" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E100" s="28" t="inlineStr">
+      <c r="E104" s="30" t="inlineStr">
         <is>
           <t>1 (row=row_i)</t>
         </is>
       </c>
-      <c r="F100" s="28" t="inlineStr">
+      <c r="F104" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="28" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B101" s="28" t="inlineStr">
+      <c r="B105" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C101" s="28" t="inlineStr">
+      <c r="C105" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D101" s="28" t="inlineStr">
+      <c r="D105" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E101" s="28" t="inlineStr">
+      <c r="E105" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F101" s="28" t="inlineStr">
+      <c r="F105" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="28" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B102" s="28" t="inlineStr">
+      <c r="B106" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C102" s="28" t="inlineStr">
+      <c r="C106" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D102" s="28" t="inlineStr">
+      <c r="D106" s="30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E102" s="28" t="inlineStr">
+      <c r="E106" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F102" s="28" t="inlineStr">
+      <c r="F106" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="28" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B103" s="28" t="inlineStr">
+      <c r="B107" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C103" s="28" t="inlineStr">
+      <c r="C107" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D103" s="28" t="inlineStr">
+      <c r="D107" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E103" s="28" t="inlineStr">
+      <c r="E107" s="30" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F103" s="28" t="inlineStr">
+      <c r="F107" s="30" t="inlineStr">
         <is>
           <t>set_ap_i</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="28" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B104" s="28" t="inlineStr">
+      <c r="B108" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C104" s="28" t="inlineStr">
+      <c r="C108" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D104" s="28" t="inlineStr">
+      <c r="D108" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E104" s="28" t="inlineStr">
+      <c r="E108" s="30" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
       </c>
-      <c r="F104" s="28" t="inlineStr">
+      <c r="F108" s="30" t="inlineStr">
         <is>
           <t>unchanged</t>
         </is>
@@ -8738,7 +8829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8799,7 +8890,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
@@ -8825,56 +8916,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Accepting a refresh grant depends only on the grant arriving and there being a refresh still owed. The burst counter does not appear because it is loaded, not tested, at this edge.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8886,435 +8977,456 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      grant &amp; pend_nz</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>refresh_drain_active</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:126</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>w_drain_active = (r_burst_remaining &gt; 0) &amp;&amp; (r_pending &gt; 0) &amp;&amp; refresh_req_o</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>rows = rem_nz/pend_nz   cols = req_o</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1): holding the arbiter in the refresh branch requires quota AND owed refreshes AND the REGISTERED request. The req_o term is not redundant -- a postponed backlog withholds req_o while pending is non-zero, and without this term the drain window would open anyway and defeat the postpone credit.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) req_o does NOT follow pend_nz: a postponed backlog withholds the registered request while pending is non-zero. That is exactly why the term is in the equation, so all combinations occur.</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:186-192</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="22" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Drain is active exactly while the burst has commands left, refreshes are still owed, and the request line is up. tREFI does not appear: it sets r_pending elsewhere, and this map is about draining what is already owed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B32" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B33" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B34" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="23" t="n">
+      <c r="B35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B35" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="B36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: rem_nz &amp; pend_nz &amp; req_o</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      rem_nz &amp; pend_nz &amp; req_o</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>r_pending next-value</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>refresh_ctrl.sv:98-108</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>refresh_req_o (registered) = pending&gt;0. Saturation at 8 = a JEDEC retention violation looming — the arbiter must be serving REFs.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="27" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>enable &amp;&amp; expired</t>
         </is>
       </c>
-      <c r="B42" s="27" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>w_grant_accept</t>
         </is>
       </c>
-      <c r="C42" s="27" t="inlineStr">
+      <c r="C44" s="29" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="28" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="28" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C43" s="28" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>min(pending+1, 8)  (postpone cap)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="28" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>pending-1</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="28" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B45" s="28" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C45" s="28" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>pending (net zero)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="28" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B46" s="28" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C46" s="28" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>busy_o</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>pumice_mem_cmd_scheduler.sv</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>busy = !init_done || refresh_req || w_cmd_rd_valid || (|w_bank_row_active[0])</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>rows = init_done/refresh_req   cols = cmd_rd_valid/any_row_active</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Zero ONLY at (1,0,0,0): init complete, no refresh owed, cmd FIFO empty, all rows closed. 15 of 16 cells are 1 — busy is the OR-reduce of everything in flight.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="21" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    (independent) cmd_rd_valid is the command FIFO's read-valid and is not gated on init_done, and any_row_active is a registered image, so all sixteen combinations are reachable.</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>pumice_mem_cmd_scheduler.sv:529,576</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="21" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
-        </is>
-      </c>
-    </row>
     <row r="58">
-      <c r="B58" s="22" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: Busy is the OR of every reason the controller cannot be considered idle: init incomplete, a refresh outstanding, a command still in the read path, or any row left open. The bank index is folded into any_row_active because busy is a whole-controller output -- WHICH bank is open cannot change the answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C58" s="22" t="inlineStr">
+      <c r="C60" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D58" s="22" t="inlineStr">
+      <c r="D60" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E58" s="22" t="inlineStr">
+      <c r="E60" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B59" s="23" t="n">
+      <c r="B61" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="23" t="n">
+      <c r="C61" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="23" t="n">
+      <c r="D61" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="23" t="n">
+      <c r="E61" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="22" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B60" s="23" t="n">
+      <c r="B62" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="23" t="n">
+      <c r="C62" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D60" s="23" t="n">
+      <c r="D62" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="23" t="n">
+      <c r="E62" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="22" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B61" s="23" t="n">
+      <c r="B63" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="23" t="n">
+      <c r="C63" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="23" t="n">
+      <c r="D63" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="23" t="n">
+      <c r="E63" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="22" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B62" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="23" t="n">
+      <c r="B64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="23" t="n">
+      <c r="D64" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="23" t="n">
+      <c r="E64" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: !init_done  |  any_row_active  |  cmd_rd_valid  |  refresh_req</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="21" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      !init_done | refresh_req | cmd_rd_valid | any_row_active</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
         </is>
       </c>
     </row>
